--- a/demo_data/sectors/uretim_sanayi/sales_ledger.xlsx
+++ b/demo_data/sectors/uretim_sanayi/sales_ledger.xlsx
@@ -470,12 +470,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Maliyet</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Net Satış Tutarı</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Maliyet</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -510,19 +510,19 @@
         <v>650</v>
       </c>
       <c r="F2" t="n">
-        <v>20781.35</v>
+        <v>20101.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H2" t="n">
-        <v>20781.35</v>
+        <v>13607.18</v>
       </c>
       <c r="I2" t="n">
-        <v>14067.38</v>
+        <v>20101.62</v>
       </c>
       <c r="J2" t="n">
-        <v>20781.35</v>
+        <v>20101.62</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -549,19 +549,19 @@
         <v>1200</v>
       </c>
       <c r="F3" t="n">
-        <v>72894.58</v>
+        <v>70509.95</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>72894.58</v>
+        <v>48181.8</v>
       </c>
       <c r="I3" t="n">
-        <v>49811.3</v>
+        <v>70509.95</v>
       </c>
       <c r="J3" t="n">
-        <v>72894.58</v>
+        <v>70509.95</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -588,19 +588,19 @@
         <v>21500</v>
       </c>
       <c r="F4" t="n">
-        <v>206214.93</v>
+        <v>199468.95</v>
       </c>
       <c r="G4" t="n">
-        <v>16497.19</v>
+        <v>8743.889999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>189717.74</v>
+        <v>131742.28</v>
       </c>
       <c r="I4" t="n">
-        <v>136197.77</v>
+        <v>190725.06</v>
       </c>
       <c r="J4" t="n">
-        <v>189717.74</v>
+        <v>190725.06</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -627,19 +627,19 @@
         <v>8900</v>
       </c>
       <c r="F5" t="n">
-        <v>142272.32</v>
+        <v>137618.11</v>
       </c>
       <c r="G5" t="n">
-        <v>17072.68</v>
+        <v>3619.56</v>
       </c>
       <c r="H5" t="n">
-        <v>125199.64</v>
+        <v>91229.98</v>
       </c>
       <c r="I5" t="n">
-        <v>94315.36</v>
+        <v>133998.55</v>
       </c>
       <c r="J5" t="n">
-        <v>125199.64</v>
+        <v>133998.55</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,7 +648,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -666,19 +666,19 @@
         <v>8900</v>
       </c>
       <c r="F6" t="n">
-        <v>256090.17</v>
+        <v>247712.6</v>
       </c>
       <c r="G6" t="n">
-        <v>20487.21</v>
+        <v>10858.69</v>
       </c>
       <c r="H6" t="n">
-        <v>235602.96</v>
+        <v>164213.97</v>
       </c>
       <c r="I6" t="n">
-        <v>169767.64</v>
+        <v>236853.91</v>
       </c>
       <c r="J6" t="n">
-        <v>235602.96</v>
+        <v>236853.91</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -705,19 +705,19 @@
         <v>2400</v>
       </c>
       <c r="F7" t="n">
-        <v>53711.8</v>
+        <v>51954.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4296.94</v>
+        <v>2277.48</v>
       </c>
       <c r="H7" t="n">
-        <v>49414.85</v>
+        <v>32471.69</v>
       </c>
       <c r="I7" t="n">
-        <v>33569.87</v>
+        <v>49677.22</v>
       </c>
       <c r="J7" t="n">
-        <v>49414.85</v>
+        <v>49677.22</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -744,19 +744,19 @@
         <v>1200</v>
       </c>
       <c r="F8" t="n">
-        <v>88240.81</v>
+        <v>85354.14999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>2647.22</v>
+        <v>1496.63</v>
       </c>
       <c r="H8" t="n">
-        <v>85593.58</v>
+        <v>58325.34</v>
       </c>
       <c r="I8" t="n">
-        <v>60297.89</v>
+        <v>83857.52</v>
       </c>
       <c r="J8" t="n">
-        <v>85593.58</v>
+        <v>83857.52</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -783,19 +783,19 @@
         <v>650</v>
       </c>
       <c r="F9" t="n">
-        <v>31172.02</v>
+        <v>30152.28</v>
       </c>
       <c r="G9" t="n">
-        <v>2493.76</v>
+        <v>1321.75</v>
       </c>
       <c r="H9" t="n">
-        <v>28678.26</v>
+        <v>20410.78</v>
       </c>
       <c r="I9" t="n">
-        <v>21101.06</v>
+        <v>28830.53</v>
       </c>
       <c r="J9" t="n">
-        <v>28678.26</v>
+        <v>28830.53</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -822,19 +822,19 @@
         <v>4200</v>
       </c>
       <c r="F10" t="n">
-        <v>107423.59</v>
+        <v>103909.41</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>107423.59</v>
+        <v>69272.94</v>
       </c>
       <c r="I10" t="n">
-        <v>71615.73</v>
+        <v>103909.41</v>
       </c>
       <c r="J10" t="n">
-        <v>107423.59</v>
+        <v>103909.41</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -861,19 +861,19 @@
         <v>650</v>
       </c>
       <c r="F11" t="n">
-        <v>2078.13</v>
+        <v>2010.15</v>
       </c>
       <c r="G11" t="n">
-        <v>166.25</v>
+        <v>88.12</v>
       </c>
       <c r="H11" t="n">
-        <v>1911.88</v>
+        <v>1360.72</v>
       </c>
       <c r="I11" t="n">
-        <v>1406.74</v>
+        <v>1922.03</v>
       </c>
       <c r="J11" t="n">
-        <v>1911.88</v>
+        <v>1922.03</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -900,19 +900,19 @@
         <v>1200</v>
       </c>
       <c r="F12" t="n">
-        <v>72894.58</v>
+        <v>70509.95</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>72894.58</v>
+        <v>48181.8</v>
       </c>
       <c r="I12" t="n">
-        <v>49811.3</v>
+        <v>70509.95</v>
       </c>
       <c r="J12" t="n">
-        <v>72894.58</v>
+        <v>70509.95</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -939,19 +939,19 @@
         <v>4200</v>
       </c>
       <c r="F13" t="n">
-        <v>308842.83</v>
+        <v>298739.54</v>
       </c>
       <c r="G13" t="n">
-        <v>37061.14</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>271781.69</v>
+        <v>199159.69</v>
       </c>
       <c r="I13" t="n">
-        <v>205895.22</v>
+        <v>298739.54</v>
       </c>
       <c r="J13" t="n">
-        <v>271781.69</v>
+        <v>298739.54</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F14" t="n">
-        <v>11509.67</v>
+        <v>25977.35</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>455.5</v>
       </c>
       <c r="H14" t="n">
-        <v>11509.67</v>
+        <v>17318.23</v>
       </c>
       <c r="I14" t="n">
-        <v>7864.94</v>
+        <v>25521.85</v>
       </c>
       <c r="J14" t="n">
-        <v>11509.67</v>
+        <v>25521.85</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F15" t="n">
-        <v>6234.4</v>
+        <v>33399.45</v>
       </c>
       <c r="G15" t="n">
-        <v>498.75</v>
+        <v>878.46</v>
       </c>
       <c r="H15" t="n">
-        <v>5735.65</v>
+        <v>22822.96</v>
       </c>
       <c r="I15" t="n">
-        <v>4220.21</v>
+        <v>32520.99</v>
       </c>
       <c r="J15" t="n">
-        <v>5735.65</v>
+        <v>32520.99</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1043,32 +1043,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F16" t="n">
-        <v>1083187.89</v>
+        <v>660566.9300000001</v>
       </c>
       <c r="G16" t="n">
-        <v>54159.39</v>
+        <v>28956.52</v>
       </c>
       <c r="H16" t="n">
-        <v>1029028.5</v>
+        <v>437903.92</v>
       </c>
       <c r="I16" t="n">
-        <v>689301.39</v>
+        <v>631610.41</v>
       </c>
       <c r="J16" t="n">
-        <v>1029028.5</v>
+        <v>631610.41</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
-        <v>8900</v>
+        <v>21500</v>
       </c>
       <c r="F17" t="n">
-        <v>682907.12</v>
+        <v>531917.1899999999</v>
       </c>
       <c r="G17" t="n">
-        <v>54632.57</v>
+        <v>13990.23</v>
       </c>
       <c r="H17" t="n">
-        <v>628274.55</v>
+        <v>351312.75</v>
       </c>
       <c r="I17" t="n">
-        <v>452713.71</v>
+        <v>517926.96</v>
       </c>
       <c r="J17" t="n">
-        <v>628274.55</v>
+        <v>517926.96</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F18" t="n">
-        <v>549906.49</v>
+        <v>51954.7</v>
       </c>
       <c r="G18" t="n">
-        <v>27495.32</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>522411.16</v>
+        <v>32471.69</v>
       </c>
       <c r="I18" t="n">
-        <v>363194.05</v>
+        <v>51954.7</v>
       </c>
       <c r="J18" t="n">
-        <v>522411.16</v>
+        <v>51954.7</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1167,25 +1167,25 @@
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>2400</v>
       </c>
       <c r="F19" t="n">
-        <v>53711.8</v>
+        <v>89065.2</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2342.55</v>
       </c>
       <c r="H19" t="n">
-        <v>53711.8</v>
+        <v>55665.75</v>
       </c>
       <c r="I19" t="n">
-        <v>33569.87</v>
+        <v>86722.64999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>53711.8</v>
+        <v>86722.64999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F20" t="n">
-        <v>92077.37</v>
+        <v>1595751.58</v>
       </c>
       <c r="G20" t="n">
-        <v>4603.87</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>87473.5</v>
+        <v>1053938.26</v>
       </c>
       <c r="I20" t="n">
-        <v>57548.35</v>
+        <v>1595751.58</v>
       </c>
       <c r="J20" t="n">
-        <v>87473.5</v>
+        <v>1595751.58</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F21" t="n">
-        <v>1649719.46</v>
+        <v>25977.35</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>683.24</v>
       </c>
       <c r="H21" t="n">
-        <v>1649719.46</v>
+        <v>17318.23</v>
       </c>
       <c r="I21" t="n">
-        <v>1089582.15</v>
+        <v>25294.11</v>
       </c>
       <c r="J21" t="n">
-        <v>1649719.46</v>
+        <v>25294.11</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F22" t="n">
-        <v>26855.9</v>
+        <v>8040.61</v>
       </c>
       <c r="G22" t="n">
-        <v>1342.79</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>25513.1</v>
+        <v>5442.87</v>
       </c>
       <c r="I22" t="n">
-        <v>17903.93</v>
+        <v>8040.61</v>
       </c>
       <c r="J22" t="n">
-        <v>25513.1</v>
+        <v>8040.61</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F23" t="n">
-        <v>8312.540000000001</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1756.91</v>
       </c>
       <c r="H23" t="n">
-        <v>8312.540000000001</v>
+        <v>45645.92</v>
       </c>
       <c r="I23" t="n">
-        <v>5626.95</v>
+        <v>65041.99</v>
       </c>
       <c r="J23" t="n">
-        <v>8312.540000000001</v>
+        <v>65041.99</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F24" t="n">
-        <v>69058.02</v>
+        <v>44532.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3452.9</v>
+        <v>780.85</v>
       </c>
       <c r="H24" t="n">
-        <v>65605.12</v>
+        <v>27832.88</v>
       </c>
       <c r="I24" t="n">
-        <v>47189.65</v>
+        <v>43751.75</v>
       </c>
       <c r="J24" t="n">
-        <v>65605.12</v>
+        <v>43751.75</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F25" t="n">
-        <v>46038.68</v>
+        <v>11133.15</v>
       </c>
       <c r="G25" t="n">
-        <v>1381.16</v>
+        <v>292.82</v>
       </c>
       <c r="H25" t="n">
-        <v>44657.52</v>
+        <v>7607.65</v>
       </c>
       <c r="I25" t="n">
-        <v>28774.18</v>
+        <v>10840.33</v>
       </c>
       <c r="J25" t="n">
-        <v>44657.52</v>
+        <v>10840.33</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F26" t="n">
-        <v>11509.67</v>
+        <v>25977.35</v>
       </c>
       <c r="G26" t="n">
-        <v>575.48</v>
+        <v>1138.74</v>
       </c>
       <c r="H26" t="n">
-        <v>10934.19</v>
+        <v>17318.23</v>
       </c>
       <c r="I26" t="n">
-        <v>7864.94</v>
+        <v>24838.61</v>
       </c>
       <c r="J26" t="n">
-        <v>10934.19</v>
+        <v>24838.61</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F27" t="n">
-        <v>26855.9</v>
+        <v>17163.61</v>
       </c>
       <c r="G27" t="n">
-        <v>3222.71</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>23633.19</v>
+        <v>11597.03</v>
       </c>
       <c r="I27" t="n">
-        <v>17903.93</v>
+        <v>17163.61</v>
       </c>
       <c r="J27" t="n">
-        <v>23633.19</v>
+        <v>17163.61</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F28" t="n">
-        <v>17744.08</v>
+        <v>118753.61</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3123.4</v>
       </c>
       <c r="H28" t="n">
-        <v>17744.08</v>
+        <v>74221</v>
       </c>
       <c r="I28" t="n">
-        <v>11989.24</v>
+        <v>115630.21</v>
       </c>
       <c r="J28" t="n">
-        <v>17744.08</v>
+        <v>115630.21</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,7 +1545,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1557,25 +1557,25 @@
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>2400</v>
       </c>
       <c r="F29" t="n">
-        <v>122769.82</v>
+        <v>14844.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6138.49</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>116631.33</v>
+        <v>9277.629999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>76731.14</v>
+        <v>14844.2</v>
       </c>
       <c r="J29" t="n">
-        <v>116631.33</v>
+        <v>14844.2</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E30" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F30" t="n">
-        <v>15346.23</v>
+        <v>74375.63</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1304.13</v>
       </c>
       <c r="H30" t="n">
-        <v>15346.23</v>
+        <v>50253.8</v>
       </c>
       <c r="I30" t="n">
-        <v>9591.389999999999</v>
+        <v>73071.5</v>
       </c>
       <c r="J30" t="n">
-        <v>15346.23</v>
+        <v>73071.5</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F31" t="n">
-        <v>76890.99000000001</v>
+        <v>664896.49</v>
       </c>
       <c r="G31" t="n">
-        <v>2306.73</v>
+        <v>17487.79</v>
       </c>
       <c r="H31" t="n">
-        <v>74584.25999999999</v>
+        <v>439140.94</v>
       </c>
       <c r="I31" t="n">
-        <v>51953.37</v>
+        <v>647408.7</v>
       </c>
       <c r="J31" t="n">
-        <v>74584.25999999999</v>
+        <v>647408.7</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,7 +1662,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1674,25 +1674,25 @@
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
         <v>21500</v>
       </c>
       <c r="F32" t="n">
-        <v>687383.11</v>
+        <v>332448.25</v>
       </c>
       <c r="G32" t="n">
-        <v>34369.16</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>653013.95</v>
+        <v>219570.47</v>
       </c>
       <c r="I32" t="n">
-        <v>453992.56</v>
+        <v>332448.25</v>
       </c>
       <c r="J32" t="n">
-        <v>653013.95</v>
+        <v>332448.25</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F33" t="n">
-        <v>343691.55</v>
+        <v>7422.1</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.35</v>
       </c>
       <c r="H33" t="n">
-        <v>343691.55</v>
+        <v>5071.77</v>
       </c>
       <c r="I33" t="n">
-        <v>226996.28</v>
+        <v>7096.75</v>
       </c>
       <c r="J33" t="n">
-        <v>343691.55</v>
+        <v>7096.75</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E34" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F34" t="n">
-        <v>7673.11</v>
+        <v>137308.86</v>
       </c>
       <c r="G34" t="n">
-        <v>613.85</v>
+        <v>2407.62</v>
       </c>
       <c r="H34" t="n">
-        <v>7059.26</v>
+        <v>92776.25</v>
       </c>
       <c r="I34" t="n">
-        <v>5243.29</v>
+        <v>134901.24</v>
       </c>
       <c r="J34" t="n">
-        <v>7059.26</v>
+        <v>134901.24</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,7 +1779,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1791,25 +1791,25 @@
         <v>45724</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
         <v>1850</v>
       </c>
       <c r="F35" t="n">
-        <v>141952.6</v>
+        <v>108702.85</v>
       </c>
       <c r="G35" t="n">
-        <v>4258.58</v>
+        <v>2859.05</v>
       </c>
       <c r="H35" t="n">
-        <v>137694.03</v>
+        <v>73447.87</v>
       </c>
       <c r="I35" t="n">
-        <v>95913.92</v>
+        <v>105843.8</v>
       </c>
       <c r="J35" t="n">
-        <v>137694.03</v>
+        <v>105843.8</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F36" t="n">
-        <v>112379.15</v>
+        <v>55047.24</v>
       </c>
       <c r="G36" t="n">
-        <v>5618.96</v>
+        <v>2413.04</v>
       </c>
       <c r="H36" t="n">
-        <v>106760.19</v>
+        <v>36491.99</v>
       </c>
       <c r="I36" t="n">
-        <v>75931.85000000001</v>
+        <v>52634.2</v>
       </c>
       <c r="J36" t="n">
-        <v>106760.19</v>
+        <v>52634.2</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1869,25 +1869,25 @@
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
         <v>8900</v>
       </c>
       <c r="F37" t="n">
-        <v>56908.93</v>
+        <v>82570.87</v>
       </c>
       <c r="G37" t="n">
-        <v>4552.71</v>
+        <v>3619.56</v>
       </c>
       <c r="H37" t="n">
-        <v>52356.21</v>
+        <v>54737.99</v>
       </c>
       <c r="I37" t="n">
-        <v>37726.14</v>
+        <v>78951.31</v>
       </c>
       <c r="J37" t="n">
-        <v>52356.21</v>
+        <v>78951.31</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1901,32 +1901,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F38" t="n">
-        <v>85363.39</v>
+        <v>48243.65</v>
       </c>
       <c r="G38" t="n">
-        <v>6829.07</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>78534.32000000001</v>
+        <v>32966.5</v>
       </c>
       <c r="I38" t="n">
-        <v>56589.21</v>
+        <v>48243.65</v>
       </c>
       <c r="J38" t="n">
-        <v>78534.32000000001</v>
+        <v>48243.65</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1947,25 +1947,25 @@
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E39" t="n">
         <v>1200</v>
       </c>
       <c r="F39" t="n">
-        <v>49875.24</v>
+        <v>70509.95</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3090.86</v>
       </c>
       <c r="H39" t="n">
-        <v>49875.24</v>
+        <v>48181.8</v>
       </c>
       <c r="I39" t="n">
-        <v>34081.41</v>
+        <v>67419.09</v>
       </c>
       <c r="J39" t="n">
-        <v>49875.24</v>
+        <v>67419.09</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F40" t="n">
-        <v>72894.58</v>
+        <v>181841.46</v>
       </c>
       <c r="G40" t="n">
-        <v>5831.57</v>
+        <v>7971.18</v>
       </c>
       <c r="H40" t="n">
-        <v>67063.00999999999</v>
+        <v>121227.64</v>
       </c>
       <c r="I40" t="n">
-        <v>49811.3</v>
+        <v>173870.28</v>
       </c>
       <c r="J40" t="n">
-        <v>67063.00999999999</v>
+        <v>173870.28</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E41" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F41" t="n">
-        <v>187991.29</v>
+        <v>18091.37</v>
       </c>
       <c r="G41" t="n">
-        <v>22558.95</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>165432.33</v>
+        <v>12246.47</v>
       </c>
       <c r="I41" t="n">
-        <v>125327.52</v>
+        <v>18091.37</v>
       </c>
       <c r="J41" t="n">
-        <v>165432.33</v>
+        <v>18091.37</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2064,25 +2064,25 @@
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
         <v>650</v>
       </c>
       <c r="F42" t="n">
-        <v>18703.21</v>
+        <v>16081.22</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>281.97</v>
       </c>
       <c r="H42" t="n">
-        <v>18703.21</v>
+        <v>10885.75</v>
       </c>
       <c r="I42" t="n">
-        <v>12660.64</v>
+        <v>15799.25</v>
       </c>
       <c r="J42" t="n">
-        <v>18703.21</v>
+        <v>15799.25</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E43" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F43" t="n">
-        <v>16625.08</v>
+        <v>605519.6899999999</v>
       </c>
       <c r="G43" t="n">
-        <v>498.75</v>
+        <v>10617.39</v>
       </c>
       <c r="H43" t="n">
-        <v>16126.33</v>
+        <v>401411.93</v>
       </c>
       <c r="I43" t="n">
-        <v>11253.9</v>
+        <v>594902.3</v>
       </c>
       <c r="J43" t="n">
-        <v>16126.33</v>
+        <v>594902.3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F44" t="n">
-        <v>625998.2</v>
+        <v>50253.8</v>
       </c>
       <c r="G44" t="n">
-        <v>75119.78</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>550878.41</v>
+        <v>34017.96</v>
       </c>
       <c r="I44" t="n">
-        <v>414987.57</v>
+        <v>50253.8</v>
       </c>
       <c r="J44" t="n">
-        <v>550878.41</v>
+        <v>50253.8</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2181,25 +2181,25 @@
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
         <v>21500</v>
       </c>
       <c r="F45" t="n">
-        <v>756121.42</v>
+        <v>1329792.99</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>58292.62</v>
       </c>
       <c r="H45" t="n">
-        <v>756121.42</v>
+        <v>878281.88</v>
       </c>
       <c r="I45" t="n">
-        <v>499391.82</v>
+        <v>1271500.37</v>
       </c>
       <c r="J45" t="n">
-        <v>756121.42</v>
+        <v>1271500.37</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F46" t="n">
-        <v>1374766.21</v>
+        <v>233796.16</v>
       </c>
       <c r="G46" t="n">
-        <v>109981.3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1264784.92</v>
+        <v>155864.11</v>
       </c>
       <c r="I46" t="n">
-        <v>907985.13</v>
+        <v>233796.16</v>
       </c>
       <c r="J46" t="n">
-        <v>1264784.92</v>
+        <v>233796.16</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F47" t="n">
-        <v>241703.08</v>
+        <v>238125.72</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>4175.38</v>
       </c>
       <c r="H47" t="n">
-        <v>241703.08</v>
+        <v>151534.55</v>
       </c>
       <c r="I47" t="n">
-        <v>161135.39</v>
+        <v>233950.34</v>
       </c>
       <c r="J47" t="n">
-        <v>241703.08</v>
+        <v>233950.34</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F48" t="n">
-        <v>246179.07</v>
+        <v>103909.41</v>
       </c>
       <c r="G48" t="n">
-        <v>7385.37</v>
+        <v>1821.98</v>
       </c>
       <c r="H48" t="n">
-        <v>238793.69</v>
+        <v>69272.94</v>
       </c>
       <c r="I48" t="n">
-        <v>156659.41</v>
+        <v>102087.43</v>
       </c>
       <c r="J48" t="n">
-        <v>238793.69</v>
+        <v>102087.43</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E49" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F49" t="n">
-        <v>107423.59</v>
+        <v>412854.33</v>
       </c>
       <c r="G49" t="n">
-        <v>3222.71</v>
+        <v>18097.82</v>
       </c>
       <c r="H49" t="n">
-        <v>104200.88</v>
+        <v>273689.95</v>
       </c>
       <c r="I49" t="n">
-        <v>71615.73</v>
+        <v>394756.51</v>
       </c>
       <c r="J49" t="n">
-        <v>104200.88</v>
+        <v>394756.51</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F50" t="n">
-        <v>426816.95</v>
+        <v>952502.88</v>
       </c>
       <c r="G50" t="n">
-        <v>34145.36</v>
+        <v>41753.78</v>
       </c>
       <c r="H50" t="n">
-        <v>392671.6</v>
+        <v>606138.2</v>
       </c>
       <c r="I50" t="n">
-        <v>282946.07</v>
+        <v>910749.1</v>
       </c>
       <c r="J50" t="n">
-        <v>392671.6</v>
+        <v>910749.1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2415,25 +2415,25 @@
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E51" t="n">
         <v>15400</v>
       </c>
       <c r="F51" t="n">
-        <v>984716.26</v>
+        <v>1047753.17</v>
       </c>
       <c r="G51" t="n">
-        <v>118165.95</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>866550.3100000001</v>
+        <v>666752.02</v>
       </c>
       <c r="I51" t="n">
-        <v>626637.62</v>
+        <v>1047753.17</v>
       </c>
       <c r="J51" t="n">
-        <v>866550.3100000001</v>
+        <v>1047753.17</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F52" t="n">
-        <v>130123.22</v>
+        <v>247712.6</v>
       </c>
       <c r="G52" t="n">
-        <v>10409.86</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>119713.36</v>
+        <v>164213.97</v>
       </c>
       <c r="I52" t="n">
-        <v>87921.10000000001</v>
+        <v>247712.6</v>
       </c>
       <c r="J52" t="n">
-        <v>119713.36</v>
+        <v>247712.6</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2493,25 +2493,25 @@
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E53" t="n">
         <v>4200</v>
       </c>
       <c r="F53" t="n">
-        <v>67139.75</v>
+        <v>311728.22</v>
       </c>
       <c r="G53" t="n">
-        <v>2014.19</v>
+        <v>13664.87</v>
       </c>
       <c r="H53" t="n">
-        <v>65125.55</v>
+        <v>207818.81</v>
       </c>
       <c r="I53" t="n">
-        <v>44759.83</v>
+        <v>298063.35</v>
       </c>
       <c r="J53" t="n">
-        <v>65125.55</v>
+        <v>298063.35</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E54" t="n">
-        <v>4200</v>
+        <v>15400</v>
       </c>
       <c r="F54" t="n">
-        <v>322270.78</v>
+        <v>476251.44</v>
       </c>
       <c r="G54" t="n">
-        <v>25781.66</v>
+        <v>20876.89</v>
       </c>
       <c r="H54" t="n">
-        <v>296489.12</v>
+        <v>303069.1</v>
       </c>
       <c r="I54" t="n">
-        <v>214847.19</v>
+        <v>455374.55</v>
       </c>
       <c r="J54" t="n">
-        <v>296489.12</v>
+        <v>455374.55</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E55" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F55" t="n">
-        <v>492358.13</v>
+        <v>14071.07</v>
       </c>
       <c r="G55" t="n">
-        <v>39388.65</v>
+        <v>246.73</v>
       </c>
       <c r="H55" t="n">
-        <v>452969.48</v>
+        <v>9525.030000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>313318.81</v>
+        <v>13824.34</v>
       </c>
       <c r="J55" t="n">
-        <v>452969.48</v>
+        <v>13824.34</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E56" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F56" t="n">
-        <v>14546.94</v>
+        <v>598406.84</v>
       </c>
       <c r="G56" t="n">
-        <v>1745.63</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>12801.31</v>
+        <v>395226.85</v>
       </c>
       <c r="I56" t="n">
-        <v>9847.16</v>
+        <v>598406.84</v>
       </c>
       <c r="J56" t="n">
-        <v>12801.31</v>
+        <v>598406.84</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F57" t="n">
-        <v>837008.83</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>41850.44</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>795158.38</v>
+        <v>41749.31</v>
       </c>
       <c r="I57" t="n">
-        <v>532641.98</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>795158.38</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E58" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F58" t="n">
-        <v>17744.08</v>
+        <v>50253.8</v>
       </c>
       <c r="G58" t="n">
-        <v>2129.29</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>15614.79</v>
+        <v>34017.96</v>
       </c>
       <c r="I58" t="n">
-        <v>11989.24</v>
+        <v>50253.8</v>
       </c>
       <c r="J58" t="n">
-        <v>15614.79</v>
+        <v>50253.8</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2727,25 +2727,25 @@
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E59" t="n">
         <v>15400</v>
       </c>
       <c r="F59" t="n">
-        <v>98471.63</v>
+        <v>285750.87</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>7515.68</v>
       </c>
       <c r="H59" t="n">
-        <v>98471.63</v>
+        <v>181841.46</v>
       </c>
       <c r="I59" t="n">
-        <v>62663.76</v>
+        <v>278235.19</v>
       </c>
       <c r="J59" t="n">
-        <v>98471.63</v>
+        <v>278235.19</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F60" t="n">
-        <v>597543.73</v>
+        <v>133597.81</v>
       </c>
       <c r="G60" t="n">
-        <v>17926.31</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>579617.42</v>
+        <v>83498.63</v>
       </c>
       <c r="I60" t="n">
-        <v>396124.5</v>
+        <v>133597.81</v>
       </c>
       <c r="J60" t="n">
-        <v>579617.42</v>
+        <v>133597.81</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E61" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F61" t="n">
-        <v>1237289.59</v>
+        <v>298739.54</v>
       </c>
       <c r="G61" t="n">
-        <v>148474.75</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1088814.84</v>
+        <v>199159.69</v>
       </c>
       <c r="I61" t="n">
-        <v>817186.61</v>
+        <v>298739.54</v>
       </c>
       <c r="J61" t="n">
-        <v>1088814.84</v>
+        <v>298739.54</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,7 +2832,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2844,25 +2844,25 @@
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E62" t="n">
         <v>1850</v>
       </c>
       <c r="F62" t="n">
-        <v>23658.77</v>
+        <v>68654.42999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3009.53</v>
       </c>
       <c r="H62" t="n">
-        <v>23658.77</v>
+        <v>46388.13</v>
       </c>
       <c r="I62" t="n">
-        <v>15985.65</v>
+        <v>65644.89999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>23658.77</v>
+        <v>65644.89999999999</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2883,25 +2883,25 @@
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E63" t="n">
         <v>8900</v>
       </c>
       <c r="F63" t="n">
-        <v>512180.34</v>
+        <v>385330.71</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>512180.34</v>
+        <v>255443.96</v>
       </c>
       <c r="I63" t="n">
-        <v>339535.28</v>
+        <v>385330.71</v>
       </c>
       <c r="J63" t="n">
-        <v>512180.34</v>
+        <v>385330.71</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,37 +2910,37 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E64" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F64" t="n">
-        <v>39484.56</v>
+        <v>571501.73</v>
       </c>
       <c r="G64" t="n">
-        <v>3158.77</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>36325.8</v>
+        <v>363682.92</v>
       </c>
       <c r="I64" t="n">
-        <v>26728.01</v>
+        <v>571501.73</v>
       </c>
       <c r="J64" t="n">
-        <v>36325.8</v>
+        <v>571501.73</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F65" t="n">
-        <v>38365.57</v>
+        <v>14071.07</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>38365.57</v>
+        <v>9525.030000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>23978.48</v>
+        <v>14071.07</v>
       </c>
       <c r="J65" t="n">
-        <v>38365.57</v>
+        <v>14071.07</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E66" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F66" t="n">
-        <v>4156.27</v>
+        <v>155864.11</v>
       </c>
       <c r="G66" t="n">
-        <v>124.69</v>
+        <v>6832.44</v>
       </c>
       <c r="H66" t="n">
-        <v>4031.58</v>
+        <v>103909.41</v>
       </c>
       <c r="I66" t="n">
-        <v>2813.48</v>
+        <v>149031.67</v>
       </c>
       <c r="J66" t="n">
-        <v>4031.58</v>
+        <v>149031.67</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E67" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F67" t="n">
-        <v>84404.25</v>
+        <v>148442.01</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>84404.25</v>
+        <v>92776.25</v>
       </c>
       <c r="I67" t="n">
-        <v>57676.24</v>
+        <v>148442.01</v>
       </c>
       <c r="J67" t="n">
-        <v>84404.25</v>
+        <v>148442.01</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E68" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F68" t="n">
-        <v>153462.28</v>
+        <v>22266.3</v>
       </c>
       <c r="G68" t="n">
-        <v>18415.47</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>135046.8</v>
+        <v>15215.31</v>
       </c>
       <c r="I68" t="n">
-        <v>95913.92</v>
+        <v>22266.3</v>
       </c>
       <c r="J68" t="n">
-        <v>135046.8</v>
+        <v>22266.3</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F69" t="n">
-        <v>23019.34</v>
+        <v>7422.1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>23019.34</v>
+        <v>4638.81</v>
       </c>
       <c r="I69" t="n">
-        <v>15729.88</v>
+        <v>7422.1</v>
       </c>
       <c r="J69" t="n">
-        <v>23019.34</v>
+        <v>7422.1</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E70" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F70" t="n">
-        <v>7673.11</v>
+        <v>28142.13</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>7673.11</v>
+        <v>19050.06</v>
       </c>
       <c r="I70" t="n">
-        <v>4795.7</v>
+        <v>28142.13</v>
       </c>
       <c r="J70" t="n">
-        <v>7673.11</v>
+        <v>28142.13</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E71" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F71" t="n">
-        <v>29093.89</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="G71" t="n">
-        <v>3491.27</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>25602.62</v>
+        <v>419657.93</v>
       </c>
       <c r="I71" t="n">
-        <v>19694.33</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="J71" t="n">
-        <v>25602.62</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E72" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F72" t="n">
-        <v>34529.01</v>
+        <v>91539.24000000001</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>34529.01</v>
+        <v>61850.84</v>
       </c>
       <c r="I72" t="n">
-        <v>23594.82</v>
+        <v>91539.24000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>34529.01</v>
+        <v>91539.24000000001</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>4200</v>
+        <v>21500</v>
       </c>
       <c r="F73" t="n">
-        <v>174563.34</v>
+        <v>797875.79</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>13990.23</v>
       </c>
       <c r="H73" t="n">
-        <v>174563.34</v>
+        <v>526969.13</v>
       </c>
       <c r="I73" t="n">
-        <v>116375.56</v>
+        <v>783885.5600000001</v>
       </c>
       <c r="J73" t="n">
-        <v>174563.34</v>
+        <v>783885.5600000001</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
@@ -3315,22 +3315,22 @@
         <v>8</v>
       </c>
       <c r="E74" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F74" t="n">
-        <v>549906.49</v>
+        <v>29688.4</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>549906.49</v>
+        <v>20287.07</v>
       </c>
       <c r="I74" t="n">
-        <v>363194.05</v>
+        <v>29688.4</v>
       </c>
       <c r="J74" t="n">
-        <v>549906.49</v>
+        <v>29688.4</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F75" t="n">
-        <v>824859.73</v>
+        <v>48243.65</v>
       </c>
       <c r="G75" t="n">
-        <v>24745.79</v>
+        <v>845.92</v>
       </c>
       <c r="H75" t="n">
-        <v>800113.9399999999</v>
+        <v>32966.5</v>
       </c>
       <c r="I75" t="n">
-        <v>544791.08</v>
+        <v>47397.73</v>
       </c>
       <c r="J75" t="n">
-        <v>800113.9399999999</v>
+        <v>47397.73</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
-        <v>1200</v>
+        <v>4200</v>
       </c>
       <c r="F76" t="n">
-        <v>30692.46</v>
+        <v>324716.89</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>5693.7</v>
       </c>
       <c r="H76" t="n">
-        <v>30692.46</v>
+        <v>216477.93</v>
       </c>
       <c r="I76" t="n">
-        <v>20973.18</v>
+        <v>319023.19</v>
       </c>
       <c r="J76" t="n">
-        <v>30692.46</v>
+        <v>319023.19</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E77" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F77" t="n">
-        <v>49875.24</v>
+        <v>163286.21</v>
       </c>
       <c r="G77" t="n">
-        <v>1496.26</v>
+        <v>7157.79</v>
       </c>
       <c r="H77" t="n">
-        <v>48378.98</v>
+        <v>102053.88</v>
       </c>
       <c r="I77" t="n">
-        <v>34081.41</v>
+        <v>156128.42</v>
       </c>
       <c r="J77" t="n">
-        <v>48378.98</v>
+        <v>156128.42</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
-        <v>4200</v>
+        <v>1850</v>
       </c>
       <c r="F78" t="n">
-        <v>335698.73</v>
+        <v>22884.81</v>
       </c>
       <c r="G78" t="n">
-        <v>10070.96</v>
+        <v>401.27</v>
       </c>
       <c r="H78" t="n">
-        <v>325627.76</v>
+        <v>15462.71</v>
       </c>
       <c r="I78" t="n">
-        <v>223799.15</v>
+        <v>22483.54</v>
       </c>
       <c r="J78" t="n">
-        <v>325627.76</v>
+        <v>22483.54</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F79" t="n">
-        <v>168808.5</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>13504.68</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>155303.82</v>
+        <v>60613.82</v>
       </c>
       <c r="I79" t="n">
-        <v>105505.31</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>155303.82</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F80" t="n">
-        <v>23658.77</v>
+        <v>89065.2</v>
       </c>
       <c r="G80" t="n">
-        <v>709.76</v>
+        <v>1561.7</v>
       </c>
       <c r="H80" t="n">
-        <v>22949</v>
+        <v>55665.75</v>
       </c>
       <c r="I80" t="n">
-        <v>15985.65</v>
+        <v>87503.5</v>
       </c>
       <c r="J80" t="n">
-        <v>22949</v>
+        <v>87503.5</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E81" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F81" t="n">
-        <v>98471.63</v>
+        <v>168852.78</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>7401.81</v>
       </c>
       <c r="H81" t="n">
-        <v>98471.63</v>
+        <v>112568.52</v>
       </c>
       <c r="I81" t="n">
-        <v>62663.76</v>
+        <v>161450.97</v>
       </c>
       <c r="J81" t="n">
-        <v>98471.63</v>
+        <v>161450.97</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F82" t="n">
-        <v>92077.37</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>11049.28</v>
+        <v>2505.23</v>
       </c>
       <c r="H82" t="n">
-        <v>81028.08</v>
+        <v>60613.82</v>
       </c>
       <c r="I82" t="n">
-        <v>57548.35</v>
+        <v>92745.06</v>
       </c>
       <c r="J82" t="n">
-        <v>81028.08</v>
+        <v>92745.06</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E83" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F83" t="n">
-        <v>29093.89</v>
+        <v>44532.6</v>
       </c>
       <c r="G83" t="n">
-        <v>2327.51</v>
+        <v>1171.27</v>
       </c>
       <c r="H83" t="n">
-        <v>26766.38</v>
+        <v>30430.61</v>
       </c>
       <c r="I83" t="n">
-        <v>19694.33</v>
+        <v>43361.33</v>
       </c>
       <c r="J83" t="n">
-        <v>26766.38</v>
+        <v>43361.33</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E84" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F84" t="n">
-        <v>174563.34</v>
+        <v>40203.04</v>
       </c>
       <c r="G84" t="n">
-        <v>13965.07</v>
+        <v>704.9299999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>160598.27</v>
+        <v>27214.37</v>
       </c>
       <c r="I84" t="n">
-        <v>116375.56</v>
+        <v>39498.11</v>
       </c>
       <c r="J84" t="n">
-        <v>160598.27</v>
+        <v>39498.11</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E85" t="n">
-        <v>15400</v>
+        <v>4200</v>
       </c>
       <c r="F85" t="n">
-        <v>98471.63</v>
+        <v>311728.22</v>
       </c>
       <c r="G85" t="n">
-        <v>11816.6</v>
+        <v>5465.95</v>
       </c>
       <c r="H85" t="n">
-        <v>86655.03</v>
+        <v>207818.81</v>
       </c>
       <c r="I85" t="n">
-        <v>62663.76</v>
+        <v>306262.27</v>
       </c>
       <c r="J85" t="n">
-        <v>86655.03</v>
+        <v>306262.27</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E86" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F86" t="n">
-        <v>100549.76</v>
+        <v>1047753.17</v>
       </c>
       <c r="G86" t="n">
-        <v>8043.98</v>
+        <v>27557.5</v>
       </c>
       <c r="H86" t="n">
-        <v>92505.78</v>
+        <v>666752.02</v>
       </c>
       <c r="I86" t="n">
-        <v>67939.03</v>
+        <v>1020195.67</v>
       </c>
       <c r="J86" t="n">
-        <v>92505.78</v>
+        <v>1020195.67</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E87" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F87" t="n">
-        <v>46038.68</v>
+        <v>170708.31</v>
       </c>
       <c r="G87" t="n">
-        <v>2301.93</v>
+        <v>2993.26</v>
       </c>
       <c r="H87" t="n">
-        <v>43736.75</v>
+        <v>106692.69</v>
       </c>
       <c r="I87" t="n">
-        <v>31459.77</v>
+        <v>167715.05</v>
       </c>
       <c r="J87" t="n">
-        <v>43736.75</v>
+        <v>167715.05</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E88" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F88" t="n">
-        <v>41562.7</v>
+        <v>192665.36</v>
       </c>
       <c r="G88" t="n">
-        <v>1246.88</v>
+        <v>5067.39</v>
       </c>
       <c r="H88" t="n">
-        <v>40315.82</v>
+        <v>127721.98</v>
       </c>
       <c r="I88" t="n">
-        <v>28134.75</v>
+        <v>187597.97</v>
       </c>
       <c r="J88" t="n">
-        <v>40315.82</v>
+        <v>187597.97</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3890,32 +3890,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E89" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F89" t="n">
-        <v>322270.78</v>
+        <v>163286.21</v>
       </c>
       <c r="G89" t="n">
-        <v>9668.120000000001</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>312602.65</v>
+        <v>102053.88</v>
       </c>
       <c r="I89" t="n">
-        <v>214847.19</v>
+        <v>163286.21</v>
       </c>
       <c r="J89" t="n">
-        <v>312602.65</v>
+        <v>163286.21</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,7 +3924,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3936,25 +3936,25 @@
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E90" t="n">
         <v>15400</v>
       </c>
       <c r="F90" t="n">
-        <v>1083187.89</v>
+        <v>619126.87</v>
       </c>
       <c r="G90" t="n">
-        <v>54159.39</v>
+        <v>27139.96</v>
       </c>
       <c r="H90" t="n">
-        <v>1029028.5</v>
+        <v>393989.83</v>
       </c>
       <c r="I90" t="n">
-        <v>689301.39</v>
+        <v>591986.91</v>
       </c>
       <c r="J90" t="n">
-        <v>1029028.5</v>
+        <v>591986.91</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E91" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F91" t="n">
-        <v>176481.62</v>
+        <v>57212.02</v>
       </c>
       <c r="G91" t="n">
-        <v>5294.45</v>
+        <v>1003.18</v>
       </c>
       <c r="H91" t="n">
-        <v>171187.17</v>
+        <v>38656.77</v>
       </c>
       <c r="I91" t="n">
-        <v>110301.01</v>
+        <v>56208.84</v>
       </c>
       <c r="J91" t="n">
-        <v>171187.17</v>
+        <v>56208.84</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F92" t="n">
-        <v>199181.24</v>
+        <v>141019.91</v>
       </c>
       <c r="G92" t="n">
-        <v>9959.059999999999</v>
+        <v>6181.73</v>
       </c>
       <c r="H92" t="n">
-        <v>189222.18</v>
+        <v>88137.44</v>
       </c>
       <c r="I92" t="n">
-        <v>132041.5</v>
+        <v>134838.18</v>
       </c>
       <c r="J92" t="n">
-        <v>189222.18</v>
+        <v>134838.18</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E93" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F93" t="n">
-        <v>168808.5</v>
+        <v>30152.28</v>
       </c>
       <c r="G93" t="n">
-        <v>20257.02</v>
+        <v>793.05</v>
       </c>
       <c r="H93" t="n">
-        <v>148551.48</v>
+        <v>20410.78</v>
       </c>
       <c r="I93" t="n">
-        <v>105505.31</v>
+        <v>29359.23</v>
       </c>
       <c r="J93" t="n">
-        <v>148551.48</v>
+        <v>29359.23</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E94" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F94" t="n">
-        <v>569089.27</v>
+        <v>63087.85</v>
       </c>
       <c r="G94" t="n">
-        <v>45527.14</v>
+        <v>1659.31</v>
       </c>
       <c r="H94" t="n">
-        <v>523562.13</v>
+        <v>43110.03</v>
       </c>
       <c r="I94" t="n">
-        <v>377261.43</v>
+        <v>61428.54</v>
       </c>
       <c r="J94" t="n">
-        <v>523562.13</v>
+        <v>61428.54</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E95" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F95" t="n">
-        <v>138116.05</v>
+        <v>605519.6899999999</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>138116.05</v>
+        <v>401411.93</v>
       </c>
       <c r="I95" t="n">
-        <v>86322.53</v>
+        <v>605519.6899999999</v>
       </c>
       <c r="J95" t="n">
-        <v>138116.05</v>
+        <v>605519.6899999999</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4163,32 +4163,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E96" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F96" t="n">
-        <v>344650.69</v>
+        <v>6030.46</v>
       </c>
       <c r="G96" t="n">
-        <v>17232.53</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>327418.16</v>
+        <v>4082.16</v>
       </c>
       <c r="I96" t="n">
-        <v>219323.17</v>
+        <v>6030.46</v>
       </c>
       <c r="J96" t="n">
-        <v>327418.16</v>
+        <v>6030.46</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E97" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F97" t="n">
-        <v>31172.02</v>
+        <v>381001.15</v>
       </c>
       <c r="G97" t="n">
-        <v>1558.6</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>29613.42</v>
+        <v>242455.28</v>
       </c>
       <c r="I97" t="n">
-        <v>21101.06</v>
+        <v>381001.15</v>
       </c>
       <c r="J97" t="n">
-        <v>29613.42</v>
+        <v>381001.15</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F98" t="n">
-        <v>65221.47</v>
+        <v>11442.4</v>
       </c>
       <c r="G98" t="n">
-        <v>3261.07</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>61960.39</v>
+        <v>7731.35</v>
       </c>
       <c r="I98" t="n">
-        <v>44568</v>
+        <v>11442.4</v>
       </c>
       <c r="J98" t="n">
-        <v>61960.39</v>
+        <v>11442.4</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E99" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F99" t="n">
-        <v>625998.2</v>
+        <v>194830.14</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>5124.33</v>
       </c>
       <c r="H99" t="n">
-        <v>625998.2</v>
+        <v>129886.76</v>
       </c>
       <c r="I99" t="n">
-        <v>414987.57</v>
+        <v>189705.81</v>
       </c>
       <c r="J99" t="n">
-        <v>625998.2</v>
+        <v>189705.81</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E100" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F100" t="n">
-        <v>6234.4</v>
+        <v>85354.14999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>2244.94</v>
       </c>
       <c r="H100" t="n">
-        <v>6234.4</v>
+        <v>58325.34</v>
       </c>
       <c r="I100" t="n">
-        <v>4220.21</v>
+        <v>83109.21000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>6234.4</v>
+        <v>83109.21000000001</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,12 +4353,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
@@ -4368,22 +4368,22 @@
         <v>8</v>
       </c>
       <c r="E101" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F101" t="n">
-        <v>393886.51</v>
+        <v>59376.8</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>393886.51</v>
+        <v>37110.5</v>
       </c>
       <c r="I101" t="n">
-        <v>250655.05</v>
+        <v>59376.8</v>
       </c>
       <c r="J101" t="n">
-        <v>393886.51</v>
+        <v>59376.8</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4404,25 +4404,25 @@
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E102" t="n">
         <v>1850</v>
       </c>
       <c r="F102" t="n">
-        <v>11829.38</v>
+        <v>143030.06</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>11829.38</v>
+        <v>96641.92999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>7992.83</v>
+        <v>143030.06</v>
       </c>
       <c r="J102" t="n">
-        <v>11829.38</v>
+        <v>143030.06</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E103" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F103" t="n">
-        <v>201419.24</v>
+        <v>59376.8</v>
       </c>
       <c r="G103" t="n">
-        <v>10070.96</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>191348.27</v>
+        <v>37110.5</v>
       </c>
       <c r="I103" t="n">
-        <v>134279.49</v>
+        <v>59376.8</v>
       </c>
       <c r="J103" t="n">
-        <v>191348.27</v>
+        <v>59376.8</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F104" t="n">
-        <v>88240.81</v>
+        <v>132979.3</v>
       </c>
       <c r="G104" t="n">
-        <v>10588.9</v>
+        <v>5829.26</v>
       </c>
       <c r="H104" t="n">
-        <v>77651.91</v>
+        <v>87828.19</v>
       </c>
       <c r="I104" t="n">
-        <v>60297.89</v>
+        <v>127150.04</v>
       </c>
       <c r="J104" t="n">
-        <v>77651.91</v>
+        <v>127150.04</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E105" t="n">
-        <v>21500</v>
+        <v>4200</v>
       </c>
       <c r="F105" t="n">
-        <v>893598.04</v>
+        <v>194830.14</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>893598.04</v>
+        <v>129886.76</v>
       </c>
       <c r="I105" t="n">
-        <v>590190.33</v>
+        <v>194830.14</v>
       </c>
       <c r="J105" t="n">
-        <v>893598.04</v>
+        <v>194830.14</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E106" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F106" t="n">
-        <v>147867.3</v>
+        <v>1462772.29</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>64121.88</v>
       </c>
       <c r="H106" t="n">
-        <v>147867.3</v>
+        <v>966110.0699999999</v>
       </c>
       <c r="I106" t="n">
-        <v>99910.34</v>
+        <v>1398650.41</v>
       </c>
       <c r="J106" t="n">
-        <v>147867.3</v>
+        <v>1398650.41</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E107" t="n">
-        <v>2400</v>
+        <v>650</v>
       </c>
       <c r="F107" t="n">
-        <v>61384.91</v>
+        <v>50253.8</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>1321.75</v>
       </c>
       <c r="H107" t="n">
-        <v>61384.91</v>
+        <v>34017.96</v>
       </c>
       <c r="I107" t="n">
-        <v>38365.57</v>
+        <v>48932.05</v>
       </c>
       <c r="J107" t="n">
-        <v>61384.91</v>
+        <v>48932.05</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E108" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F108" t="n">
-        <v>137476.62</v>
+        <v>133597.81</v>
       </c>
       <c r="G108" t="n">
-        <v>10998.13</v>
+        <v>3513.82</v>
       </c>
       <c r="H108" t="n">
-        <v>126478.49</v>
+        <v>83498.63</v>
       </c>
       <c r="I108" t="n">
-        <v>90798.50999999999</v>
+        <v>130083.99</v>
       </c>
       <c r="J108" t="n">
-        <v>126478.49</v>
+        <v>130083.99</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E109" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F109" t="n">
-        <v>201419.24</v>
+        <v>660566.9300000001</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>17373.91</v>
       </c>
       <c r="H109" t="n">
-        <v>201419.24</v>
+        <v>437903.92</v>
       </c>
       <c r="I109" t="n">
-        <v>134279.49</v>
+        <v>643193.02</v>
       </c>
       <c r="J109" t="n">
-        <v>201419.24</v>
+        <v>643193.02</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E110" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F110" t="n">
-        <v>1512242.84</v>
+        <v>1190628.6</v>
       </c>
       <c r="G110" t="n">
-        <v>120979.43</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>1391263.41</v>
+        <v>757672.75</v>
       </c>
       <c r="I110" t="n">
-        <v>998783.64</v>
+        <v>1190628.6</v>
       </c>
       <c r="J110" t="n">
-        <v>1391263.41</v>
+        <v>1190628.6</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,12 +4743,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
@@ -4758,22 +4758,22 @@
         <v>25</v>
       </c>
       <c r="E111" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F111" t="n">
-        <v>51953.37</v>
+        <v>1190628.6</v>
       </c>
       <c r="G111" t="n">
-        <v>2597.67</v>
+        <v>52192.23</v>
       </c>
       <c r="H111" t="n">
-        <v>49355.71</v>
+        <v>757672.75</v>
       </c>
       <c r="I111" t="n">
-        <v>35168.44</v>
+        <v>1138436.37</v>
       </c>
       <c r="J111" t="n">
-        <v>49355.71</v>
+        <v>1138436.37</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E112" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F112" t="n">
-        <v>138116.05</v>
+        <v>33399.45</v>
       </c>
       <c r="G112" t="n">
-        <v>6905.8</v>
+        <v>878.46</v>
       </c>
       <c r="H112" t="n">
-        <v>131210.25</v>
+        <v>22822.96</v>
       </c>
       <c r="I112" t="n">
-        <v>86322.53</v>
+        <v>32520.99</v>
       </c>
       <c r="J112" t="n">
-        <v>131210.25</v>
+        <v>32520.99</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E113" t="n">
-        <v>8900</v>
+        <v>15400</v>
       </c>
       <c r="F113" t="n">
-        <v>682907.12</v>
+        <v>381001.15</v>
       </c>
       <c r="G113" t="n">
-        <v>34145.36</v>
+        <v>6680.61</v>
       </c>
       <c r="H113" t="n">
-        <v>648761.77</v>
+        <v>242455.28</v>
       </c>
       <c r="I113" t="n">
-        <v>452713.71</v>
+        <v>374320.54</v>
       </c>
       <c r="J113" t="n">
-        <v>648761.77</v>
+        <v>374320.54</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E114" t="n">
-        <v>15400</v>
+        <v>650</v>
       </c>
       <c r="F114" t="n">
-        <v>1230895.33</v>
+        <v>36182.74</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>1230895.33</v>
+        <v>24492.93</v>
       </c>
       <c r="I114" t="n">
-        <v>783297.03</v>
+        <v>36182.74</v>
       </c>
       <c r="J114" t="n">
-        <v>1230895.33</v>
+        <v>36182.74</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E115" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F115" t="n">
-        <v>1230895.33</v>
+        <v>220188.98</v>
       </c>
       <c r="G115" t="n">
-        <v>98471.63</v>
+        <v>5791.3</v>
       </c>
       <c r="H115" t="n">
-        <v>1132423.7</v>
+        <v>145967.97</v>
       </c>
       <c r="I115" t="n">
-        <v>783297.03</v>
+        <v>214397.68</v>
       </c>
       <c r="J115" t="n">
-        <v>1132423.7</v>
+        <v>214397.68</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E116" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F116" t="n">
-        <v>34529.01</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="G116" t="n">
-        <v>1726.45</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>32802.56</v>
+        <v>419657.93</v>
       </c>
       <c r="I116" t="n">
-        <v>23594.82</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="J116" t="n">
-        <v>32802.56</v>
+        <v>633043.3100000001</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4982,32 +4982,32 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F117" t="n">
-        <v>393886.51</v>
+        <v>103909.41</v>
       </c>
       <c r="G117" t="n">
-        <v>11816.6</v>
+        <v>1821.98</v>
       </c>
       <c r="H117" t="n">
-        <v>382069.91</v>
+        <v>64943.38</v>
       </c>
       <c r="I117" t="n">
-        <v>250655.05</v>
+        <v>102087.43</v>
       </c>
       <c r="J117" t="n">
-        <v>382069.91</v>
+        <v>102087.43</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E118" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F118" t="n">
-        <v>37406.43</v>
+        <v>930855.09</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>37406.43</v>
+        <v>614797.3199999999</v>
       </c>
       <c r="I118" t="n">
-        <v>25321.28</v>
+        <v>930855.09</v>
       </c>
       <c r="J118" t="n">
-        <v>37406.43</v>
+        <v>930855.09</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E119" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F119" t="n">
-        <v>227635.71</v>
+        <v>96487.31</v>
       </c>
       <c r="G119" t="n">
-        <v>11381.79</v>
+        <v>4229.6</v>
       </c>
       <c r="H119" t="n">
-        <v>216253.92</v>
+        <v>60304.57</v>
       </c>
       <c r="I119" t="n">
-        <v>150904.57</v>
+        <v>92257.71000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>216253.92</v>
+        <v>92257.71000000001</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5099,32 +5099,32 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E120" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F120" t="n">
-        <v>654452.66</v>
+        <v>143030.06</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>6269.85</v>
       </c>
       <c r="H120" t="n">
-        <v>654452.66</v>
+        <v>96641.92999999999</v>
       </c>
       <c r="I120" t="n">
-        <v>433850.64</v>
+        <v>136760.21</v>
       </c>
       <c r="J120" t="n">
-        <v>654452.66</v>
+        <v>136760.21</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F121" t="n">
-        <v>107423.59</v>
+        <v>66489.64999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>3222.71</v>
+        <v>1165.85</v>
       </c>
       <c r="H121" t="n">
-        <v>104200.88</v>
+        <v>43914.09</v>
       </c>
       <c r="I121" t="n">
-        <v>67139.75</v>
+        <v>65323.8</v>
       </c>
       <c r="J121" t="n">
-        <v>104200.88</v>
+        <v>65323.8</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,12 +5172,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
@@ -5187,22 +5187,22 @@
         <v>14</v>
       </c>
       <c r="E122" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F122" t="n">
-        <v>962336.35</v>
+        <v>103909.41</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>4554.96</v>
       </c>
       <c r="H122" t="n">
-        <v>962336.35</v>
+        <v>64943.38</v>
       </c>
       <c r="I122" t="n">
-        <v>635589.59</v>
+        <v>99354.45</v>
       </c>
       <c r="J122" t="n">
-        <v>962336.35</v>
+        <v>99354.45</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E123" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F123" t="n">
-        <v>99750.48</v>
+        <v>59376.8</v>
       </c>
       <c r="G123" t="n">
-        <v>7980.04</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>91770.44</v>
+        <v>40574.15</v>
       </c>
       <c r="I123" t="n">
-        <v>62344.05</v>
+        <v>59376.8</v>
       </c>
       <c r="J123" t="n">
-        <v>91770.44</v>
+        <v>59376.8</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E124" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F124" t="n">
-        <v>147867.3</v>
+        <v>118753.61</v>
       </c>
       <c r="G124" t="n">
-        <v>11829.38</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>136037.91</v>
+        <v>74221</v>
       </c>
       <c r="I124" t="n">
-        <v>99910.34</v>
+        <v>118753.61</v>
       </c>
       <c r="J124" t="n">
-        <v>136037.91</v>
+        <v>118753.61</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5294,32 +5294,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E125" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F125" t="n">
-        <v>68738.31</v>
+        <v>44223.35</v>
       </c>
       <c r="G125" t="n">
-        <v>2062.15</v>
+        <v>1163.14</v>
       </c>
       <c r="H125" t="n">
-        <v>66676.16</v>
+        <v>29935.8</v>
       </c>
       <c r="I125" t="n">
-        <v>45399.26</v>
+        <v>43060.21</v>
       </c>
       <c r="J125" t="n">
-        <v>66676.16</v>
+        <v>43060.21</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E126" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F126" t="n">
-        <v>107423.59</v>
+        <v>412854.33</v>
       </c>
       <c r="G126" t="n">
-        <v>8593.889999999999</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>98829.71000000001</v>
+        <v>273689.95</v>
       </c>
       <c r="I126" t="n">
-        <v>67139.75</v>
+        <v>412854.33</v>
       </c>
       <c r="J126" t="n">
-        <v>98829.71000000001</v>
+        <v>412854.33</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E127" t="n">
-        <v>1200</v>
+        <v>1850</v>
       </c>
       <c r="F127" t="n">
-        <v>61384.91</v>
+        <v>74375.63</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>3260.32</v>
       </c>
       <c r="H127" t="n">
-        <v>61384.91</v>
+        <v>50253.8</v>
       </c>
       <c r="I127" t="n">
-        <v>41946.36</v>
+        <v>71115.31</v>
       </c>
       <c r="J127" t="n">
-        <v>61384.91</v>
+        <v>71115.31</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E128" t="n">
-        <v>2400</v>
+        <v>1850</v>
       </c>
       <c r="F128" t="n">
-        <v>122769.82</v>
+        <v>17163.61</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>451.43</v>
       </c>
       <c r="H128" t="n">
-        <v>122769.82</v>
+        <v>11597.03</v>
       </c>
       <c r="I128" t="n">
-        <v>76731.14</v>
+        <v>16712.18</v>
       </c>
       <c r="J128" t="n">
-        <v>122769.82</v>
+        <v>16712.18</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E129" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F129" t="n">
-        <v>45718.97</v>
+        <v>398937.9</v>
       </c>
       <c r="G129" t="n">
-        <v>5486.28</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>40232.69</v>
+        <v>263484.56</v>
       </c>
       <c r="I129" t="n">
-        <v>30948.23</v>
+        <v>398937.9</v>
       </c>
       <c r="J129" t="n">
-        <v>40232.69</v>
+        <v>398937.9</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5496,25 +5496,25 @@
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E130" t="n">
         <v>2400</v>
       </c>
       <c r="F130" t="n">
-        <v>184154.73</v>
+        <v>81643.10000000001</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>184154.73</v>
+        <v>51026.94</v>
       </c>
       <c r="I130" t="n">
-        <v>115096.71</v>
+        <v>81643.10000000001</v>
       </c>
       <c r="J130" t="n">
-        <v>184154.73</v>
+        <v>81643.10000000001</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E131" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F131" t="n">
-        <v>343691.55</v>
+        <v>22111.67</v>
       </c>
       <c r="G131" t="n">
-        <v>27495.32</v>
+        <v>581.5700000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>316196.23</v>
+        <v>14967.9</v>
       </c>
       <c r="I131" t="n">
-        <v>226996.28</v>
+        <v>21530.1</v>
       </c>
       <c r="J131" t="n">
-        <v>316196.23</v>
+        <v>21530.1</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E132" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F132" t="n">
-        <v>76890.99000000001</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="G132" t="n">
-        <v>6151.28</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>70739.71000000001</v>
+        <v>41749.31</v>
       </c>
       <c r="I132" t="n">
-        <v>51953.37</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>70739.71000000001</v>
+        <v>66798.89999999999</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,7 +5601,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5613,25 +5613,25 @@
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E133" t="n">
         <v>1850</v>
       </c>
       <c r="F133" t="n">
-        <v>17744.08</v>
+        <v>137308.86</v>
       </c>
       <c r="G133" t="n">
-        <v>2129.29</v>
+        <v>6019.05</v>
       </c>
       <c r="H133" t="n">
-        <v>15614.79</v>
+        <v>92776.25</v>
       </c>
       <c r="I133" t="n">
-        <v>11989.24</v>
+        <v>131289.81</v>
       </c>
       <c r="J133" t="n">
-        <v>15614.79</v>
+        <v>131289.81</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,37 +5640,37 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Anadolu Sanayi Grubu A.Ş.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v>45924</v>
       </c>
       <c r="D134" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E134" t="n">
-        <v>8900</v>
+        <v>650</v>
       </c>
       <c r="F134" t="n">
-        <v>426816.95</v>
+        <v>16081.22</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>426816.95</v>
+        <v>10885.75</v>
       </c>
       <c r="I134" t="n">
-        <v>282946.07</v>
+        <v>16081.22</v>
       </c>
       <c r="J134" t="n">
-        <v>426816.95</v>
+        <v>16081.22</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E135" t="n">
-        <v>15400</v>
+        <v>1850</v>
       </c>
       <c r="F135" t="n">
-        <v>640065.5699999999</v>
+        <v>143030.06</v>
       </c>
       <c r="G135" t="n">
-        <v>19201.97</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>620863.6</v>
+        <v>96641.92999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>407314.46</v>
+        <v>143030.06</v>
       </c>
       <c r="J135" t="n">
-        <v>620863.6</v>
+        <v>143030.06</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5723,32 +5723,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E136" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F136" t="n">
-        <v>756121.42</v>
+        <v>3711.05</v>
       </c>
       <c r="G136" t="n">
-        <v>22683.64</v>
+        <v>162.68</v>
       </c>
       <c r="H136" t="n">
-        <v>733437.78</v>
+        <v>2535.88</v>
       </c>
       <c r="I136" t="n">
-        <v>499391.82</v>
+        <v>3548.37</v>
       </c>
       <c r="J136" t="n">
-        <v>733437.78</v>
+        <v>3548.37</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E137" t="n">
-        <v>2400</v>
+        <v>1200</v>
       </c>
       <c r="F137" t="n">
-        <v>69058.02</v>
+        <v>18555.25</v>
       </c>
       <c r="G137" t="n">
-        <v>3452.9</v>
+        <v>488.03</v>
       </c>
       <c r="H137" t="n">
-        <v>65605.12</v>
+        <v>12679.42</v>
       </c>
       <c r="I137" t="n">
-        <v>43161.26</v>
+        <v>18067.22</v>
       </c>
       <c r="J137" t="n">
-        <v>65605.12</v>
+        <v>18067.22</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,7 +5796,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5808,25 +5808,25 @@
         <v>45933</v>
       </c>
       <c r="D138" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E138" t="n">
         <v>4200</v>
       </c>
       <c r="F138" t="n">
-        <v>214847.19</v>
+        <v>246784.84</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>214847.19</v>
+        <v>164523.23</v>
       </c>
       <c r="I138" t="n">
-        <v>143231.46</v>
+        <v>246784.84</v>
       </c>
       <c r="J138" t="n">
-        <v>214847.19</v>
+        <v>246784.84</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E139" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F139" t="n">
-        <v>70976.3</v>
+        <v>1190628.6</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>20876.89</v>
       </c>
       <c r="H139" t="n">
-        <v>70976.3</v>
+        <v>757672.75</v>
       </c>
       <c r="I139" t="n">
-        <v>47956.96</v>
+        <v>1169751.71</v>
       </c>
       <c r="J139" t="n">
-        <v>70976.3</v>
+        <v>1169751.71</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5892,19 +5892,19 @@
         <v>4200</v>
       </c>
       <c r="F140" t="n">
-        <v>335698.73</v>
+        <v>324716.89</v>
       </c>
       <c r="G140" t="n">
-        <v>40283.85</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>295414.88</v>
+        <v>216477.93</v>
       </c>
       <c r="I140" t="n">
-        <v>223799.15</v>
+        <v>324716.89</v>
       </c>
       <c r="J140" t="n">
-        <v>295414.88</v>
+        <v>324716.89</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E141" t="n">
-        <v>1850</v>
+        <v>4200</v>
       </c>
       <c r="F141" t="n">
-        <v>47317.53</v>
+        <v>246784.84</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>47317.53</v>
+        <v>164523.23</v>
       </c>
       <c r="I141" t="n">
-        <v>31971.31</v>
+        <v>246784.84</v>
       </c>
       <c r="J141" t="n">
-        <v>47317.53</v>
+        <v>246784.84</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Gaziantep İhracat ve Toptan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E142" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F142" t="n">
-        <v>118293.84</v>
+        <v>904877.74</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>23799.66</v>
       </c>
       <c r="H142" t="n">
-        <v>118293.84</v>
+        <v>575831.29</v>
       </c>
       <c r="I142" t="n">
-        <v>79928.27</v>
+        <v>881078.08</v>
       </c>
       <c r="J142" t="n">
-        <v>118293.84</v>
+        <v>881078.08</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,37 +5991,37 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v>45943</v>
       </c>
       <c r="D143" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>8900</v>
+        <v>1200</v>
       </c>
       <c r="F143" t="n">
-        <v>455271.42</v>
+        <v>11133.15</v>
       </c>
       <c r="G143" t="n">
-        <v>54632.57</v>
+        <v>488.03</v>
       </c>
       <c r="H143" t="n">
-        <v>400638.85</v>
+        <v>7607.65</v>
       </c>
       <c r="I143" t="n">
-        <v>301809.14</v>
+        <v>10645.12</v>
       </c>
       <c r="J143" t="n">
-        <v>400638.85</v>
+        <v>10645.12</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6042,106 +6042,106 @@
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E144" t="n">
         <v>1200</v>
       </c>
       <c r="F144" t="n">
-        <v>57548.35</v>
+        <v>14844.2</v>
       </c>
       <c r="G144" t="n">
-        <v>6905.8</v>
+        <v>260.28</v>
       </c>
       <c r="H144" t="n">
-        <v>50642.55</v>
+        <v>10143.54</v>
       </c>
       <c r="I144" t="n">
-        <v>39324.71</v>
+        <v>14583.92</v>
       </c>
       <c r="J144" t="n">
-        <v>15192.77</v>
+        <v>4375.18</v>
       </c>
       <c r="K144" t="n">
-        <v>35449.79</v>
+        <v>10208.74</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E145" t="n">
-        <v>650</v>
+        <v>4200</v>
       </c>
       <c r="F145" t="n">
-        <v>12468.81</v>
+        <v>246784.84</v>
       </c>
       <c r="G145" t="n">
-        <v>997.5</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>11471.31</v>
+        <v>164523.23</v>
       </c>
       <c r="I145" t="n">
-        <v>8440.43</v>
+        <v>246784.84</v>
       </c>
       <c r="J145" t="n">
-        <v>5735.65</v>
+        <v>74035.45</v>
       </c>
       <c r="K145" t="n">
-        <v>5735.65</v>
+        <v>172749.39</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E146" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F146" t="n">
-        <v>335698.73</v>
+        <v>163286.21</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>2863.12</v>
       </c>
       <c r="H146" t="n">
-        <v>335698.73</v>
+        <v>102053.88</v>
       </c>
       <c r="I146" t="n">
-        <v>223799.15</v>
+        <v>160423.09</v>
       </c>
       <c r="J146" t="n">
-        <v>100709.62</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>234989.11</v>
+        <v>160423.09</v>
       </c>
     </row>
     <row r="147">
@@ -6152,353 +6152,353 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>1850</v>
+        <v>650</v>
       </c>
       <c r="F147" t="n">
-        <v>59146.92</v>
+        <v>2010.15</v>
       </c>
       <c r="G147" t="n">
-        <v>4731.75</v>
+        <v>52.87</v>
       </c>
       <c r="H147" t="n">
-        <v>54415.17</v>
+        <v>1360.72</v>
       </c>
       <c r="I147" t="n">
-        <v>39964.13</v>
+        <v>1957.28</v>
       </c>
       <c r="J147" t="n">
-        <v>27207.58</v>
+        <v>978.64</v>
       </c>
       <c r="K147" t="n">
-        <v>27207.58</v>
+        <v>978.64</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F148" t="n">
-        <v>99750.48</v>
+        <v>265958.6</v>
       </c>
       <c r="G148" t="n">
-        <v>11970.06</v>
+        <v>6995.11</v>
       </c>
       <c r="H148" t="n">
-        <v>87780.42</v>
+        <v>175656.38</v>
       </c>
       <c r="I148" t="n">
-        <v>62344.05</v>
+        <v>258963.49</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>129481.74</v>
       </c>
       <c r="K148" t="n">
-        <v>87780.42</v>
+        <v>129481.75</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E149" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F149" t="n">
-        <v>15346.23</v>
+        <v>1529261.93</v>
       </c>
       <c r="G149" t="n">
-        <v>1841.55</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>13504.68</v>
+        <v>1010024.16</v>
       </c>
       <c r="I149" t="n">
-        <v>10486.59</v>
+        <v>1529261.93</v>
       </c>
       <c r="J149" t="n">
-        <v>4051.4</v>
+        <v>764630.96</v>
       </c>
       <c r="K149" t="n">
-        <v>9453.280000000001</v>
+        <v>764630.97</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Akdeniz Endüstriyel Ürünler</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Gamma Endüstriyel</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E150" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F150" t="n">
-        <v>255131.03</v>
+        <v>660566.9300000001</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>28956.52</v>
       </c>
       <c r="H150" t="n">
-        <v>255131.03</v>
+        <v>437903.92</v>
       </c>
       <c r="I150" t="n">
-        <v>170087.35</v>
+        <v>631610.41</v>
       </c>
       <c r="J150" t="n">
-        <v>76539.31</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>178591.72</v>
+        <v>631610.41</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E151" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F151" t="n">
-        <v>168808.5</v>
+        <v>952502.88</v>
       </c>
       <c r="G151" t="n">
-        <v>5064.26</v>
+        <v>41753.78</v>
       </c>
       <c r="H151" t="n">
-        <v>163744.25</v>
+        <v>606138.2</v>
       </c>
       <c r="I151" t="n">
-        <v>105505.31</v>
+        <v>910749.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>163744.25</v>
+        <v>910749.1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E152" t="n">
-        <v>650</v>
+        <v>21500</v>
       </c>
       <c r="F152" t="n">
-        <v>2078.13</v>
+        <v>997344.74</v>
       </c>
       <c r="G152" t="n">
-        <v>103.91</v>
+        <v>26231.68</v>
       </c>
       <c r="H152" t="n">
-        <v>1974.23</v>
+        <v>658711.41</v>
       </c>
       <c r="I152" t="n">
-        <v>1406.74</v>
+        <v>971113.0600000001</v>
       </c>
       <c r="J152" t="n">
-        <v>592.27</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>1381.96</v>
+        <v>971113.0600000001</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E153" t="n">
-        <v>2400</v>
+        <v>15400</v>
       </c>
       <c r="F153" t="n">
-        <v>92077.37</v>
+        <v>523876.59</v>
       </c>
       <c r="G153" t="n">
-        <v>11049.28</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>81028.08</v>
+        <v>333376.01</v>
       </c>
       <c r="I153" t="n">
-        <v>57548.35</v>
+        <v>523876.59</v>
       </c>
       <c r="J153" t="n">
-        <v>24308.42</v>
+        <v>261938.3</v>
       </c>
       <c r="K153" t="n">
-        <v>56719.66</v>
+        <v>261938.29</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Adana Bölge Bayi A.Ş.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Beta Premium</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E154" t="n">
-        <v>8900</v>
+        <v>4200</v>
       </c>
       <c r="F154" t="n">
-        <v>398362.49</v>
+        <v>116898.08</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>3074.6</v>
       </c>
       <c r="H154" t="n">
-        <v>398362.49</v>
+        <v>77932.05</v>
       </c>
       <c r="I154" t="n">
-        <v>264083</v>
+        <v>113823.48</v>
       </c>
       <c r="J154" t="n">
-        <v>199181.24</v>
+        <v>34147.04</v>
       </c>
       <c r="K154" t="n">
-        <v>199181.24</v>
+        <v>79676.44</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toroslar Lojistik ve Ticaret</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E155" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F155" t="n">
-        <v>984716.26</v>
+        <v>1263303.34</v>
       </c>
       <c r="G155" t="n">
-        <v>78777.3</v>
+        <v>55377.99</v>
       </c>
       <c r="H155" t="n">
-        <v>905938.96</v>
+        <v>834367.79</v>
       </c>
       <c r="I155" t="n">
-        <v>626637.62</v>
+        <v>1207925.35</v>
       </c>
       <c r="J155" t="n">
-        <v>271781.69</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>634157.27</v>
+        <v>1207925.35</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6510,67 +6510,67 @@
         <v>45969</v>
       </c>
       <c r="D156" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E156" t="n">
         <v>2400</v>
       </c>
       <c r="F156" t="n">
-        <v>184154.73</v>
+        <v>81643.10000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>14732.38</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>169422.35</v>
+        <v>51026.94</v>
       </c>
       <c r="I156" t="n">
-        <v>115096.71</v>
+        <v>81643.10000000001</v>
       </c>
       <c r="J156" t="n">
-        <v>50826.71</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>118595.65</v>
+        <v>81643.10000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E157" t="n">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="F157" t="n">
-        <v>11509.67</v>
+        <v>12060.91</v>
       </c>
       <c r="G157" t="n">
-        <v>345.29</v>
+        <v>317.22</v>
       </c>
       <c r="H157" t="n">
-        <v>11164.38</v>
+        <v>8164.31</v>
       </c>
       <c r="I157" t="n">
-        <v>7864.94</v>
+        <v>11743.69</v>
       </c>
       <c r="J157" t="n">
-        <v>3349.31</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>7815.07</v>
+        <v>11743.69</v>
       </c>
     </row>
     <row r="158">
@@ -6581,347 +6581,347 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E158" t="n">
-        <v>21500</v>
+        <v>650</v>
       </c>
       <c r="F158" t="n">
-        <v>1306027.9</v>
+        <v>18091.37</v>
       </c>
       <c r="G158" t="n">
-        <v>104482.23</v>
+        <v>317.22</v>
       </c>
       <c r="H158" t="n">
-        <v>1201545.67</v>
+        <v>12246.47</v>
       </c>
       <c r="I158" t="n">
-        <v>862585.87</v>
+        <v>17774.15</v>
       </c>
       <c r="J158" t="n">
-        <v>600772.84</v>
+        <v>8887.08</v>
       </c>
       <c r="K158" t="n">
-        <v>600772.84</v>
+        <v>8887.07</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E159" t="n">
-        <v>650</v>
+        <v>15400</v>
       </c>
       <c r="F159" t="n">
-        <v>2078.13</v>
+        <v>857252.6</v>
       </c>
       <c r="G159" t="n">
-        <v>103.91</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>1974.23</v>
+        <v>545524.38</v>
       </c>
       <c r="I159" t="n">
-        <v>1406.74</v>
+        <v>857252.6</v>
       </c>
       <c r="J159" t="n">
-        <v>592.27</v>
+        <v>257175.78</v>
       </c>
       <c r="K159" t="n">
-        <v>1381.96</v>
+        <v>600076.8199999999</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>21500</v>
+        <v>1200</v>
       </c>
       <c r="F160" t="n">
-        <v>481168.17</v>
+        <v>11133.15</v>
       </c>
       <c r="G160" t="n">
-        <v>14435.05</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>466733.13</v>
+        <v>7607.65</v>
       </c>
       <c r="I160" t="n">
-        <v>317794.79</v>
+        <v>11133.15</v>
       </c>
       <c r="J160" t="n">
-        <v>140019.94</v>
+        <v>5566.57</v>
       </c>
       <c r="K160" t="n">
-        <v>326713.19</v>
+        <v>5566.58</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E161" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F161" t="n">
-        <v>984716.26</v>
+        <v>118753.61</v>
       </c>
       <c r="G161" t="n">
-        <v>118165.95</v>
+        <v>5205.67</v>
       </c>
       <c r="H161" t="n">
-        <v>866550.3100000001</v>
+        <v>74221</v>
       </c>
       <c r="I161" t="n">
-        <v>626637.62</v>
+        <v>113547.94</v>
       </c>
       <c r="J161" t="n">
-        <v>259965.09</v>
+        <v>56773.97</v>
       </c>
       <c r="K161" t="n">
-        <v>606585.22</v>
+        <v>56773.97</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E162" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F162" t="n">
-        <v>100549.76</v>
+        <v>85354.14999999999</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>2244.94</v>
       </c>
       <c r="H162" t="n">
-        <v>100549.76</v>
+        <v>58325.34</v>
       </c>
       <c r="I162" t="n">
-        <v>67939.03</v>
+        <v>83109.21000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>41554.61</v>
       </c>
       <c r="K162" t="n">
-        <v>100549.76</v>
+        <v>41554.6</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E163" t="n">
-        <v>2400</v>
+        <v>21500</v>
       </c>
       <c r="F163" t="n">
-        <v>122769.82</v>
+        <v>997344.74</v>
       </c>
       <c r="G163" t="n">
-        <v>9821.59</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>112948.23</v>
+        <v>658711.41</v>
       </c>
       <c r="I163" t="n">
-        <v>76731.14</v>
+        <v>997344.74</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>112948.23</v>
+        <v>997344.74</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E164" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F164" t="n">
-        <v>1443504.52</v>
+        <v>381001.15</v>
       </c>
       <c r="G164" t="n">
-        <v>173220.54</v>
+        <v>10020.91</v>
       </c>
       <c r="H164" t="n">
-        <v>1270283.98</v>
+        <v>242455.28</v>
       </c>
       <c r="I164" t="n">
-        <v>953384.38</v>
+        <v>370980.24</v>
       </c>
       <c r="J164" t="n">
-        <v>381085.19</v>
+        <v>185490.12</v>
       </c>
       <c r="K164" t="n">
-        <v>889198.79</v>
+        <v>185490.12</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E165" t="n">
-        <v>1850</v>
+        <v>1200</v>
       </c>
       <c r="F165" t="n">
-        <v>17744.08</v>
+        <v>37110.5</v>
       </c>
       <c r="G165" t="n">
-        <v>532.3200000000001</v>
+        <v>1626.77</v>
       </c>
       <c r="H165" t="n">
-        <v>17211.75</v>
+        <v>25358.84</v>
       </c>
       <c r="I165" t="n">
-        <v>11989.24</v>
+        <v>35483.73</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>10645.12</v>
       </c>
       <c r="K165" t="n">
-        <v>17211.75</v>
+        <v>24838.61</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E166" t="n">
-        <v>1200</v>
+        <v>21500</v>
       </c>
       <c r="F166" t="n">
-        <v>38365.57</v>
+        <v>1196813.69</v>
       </c>
       <c r="G166" t="n">
-        <v>4603.87</v>
+        <v>52463.36</v>
       </c>
       <c r="H166" t="n">
-        <v>33761.7</v>
+        <v>790453.6899999999</v>
       </c>
       <c r="I166" t="n">
-        <v>26216.47</v>
+        <v>1144350.33</v>
       </c>
       <c r="J166" t="n">
-        <v>16880.85</v>
+        <v>343305.1</v>
       </c>
       <c r="K166" t="n">
-        <v>16880.85</v>
+        <v>801045.23</v>
       </c>
     </row>
     <row r="167">
@@ -6932,41 +6932,41 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Parça Servis Paketi</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E167" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F167" t="n">
-        <v>1237289.59</v>
+        <v>178130.41</v>
       </c>
       <c r="G167" t="n">
-        <v>98983.17</v>
+        <v>7808.5</v>
       </c>
       <c r="H167" t="n">
-        <v>1138306.43</v>
+        <v>111331.51</v>
       </c>
       <c r="I167" t="n">
-        <v>817186.61</v>
+        <v>170321.91</v>
       </c>
       <c r="J167" t="n">
-        <v>341491.93</v>
+        <v>51096.57</v>
       </c>
       <c r="K167" t="n">
-        <v>796814.5</v>
+        <v>119225.34</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>İç Anadolu Tüketim Malları</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6978,28 +6978,28 @@
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E168" t="n">
         <v>650</v>
       </c>
       <c r="F168" t="n">
-        <v>24937.62</v>
+        <v>46233.5</v>
       </c>
       <c r="G168" t="n">
-        <v>2992.51</v>
+        <v>1216.01</v>
       </c>
       <c r="H168" t="n">
-        <v>21945.11</v>
+        <v>31296.52</v>
       </c>
       <c r="I168" t="n">
-        <v>16880.85</v>
+        <v>45017.49</v>
       </c>
       <c r="J168" t="n">
-        <v>6583.53</v>
+        <v>13505.25</v>
       </c>
       <c r="K168" t="n">
-        <v>15361.57</v>
+        <v>31512.24</v>
       </c>
     </row>
     <row r="169">
@@ -7023,28 +7023,28 @@
         <v>15400</v>
       </c>
       <c r="F169" t="n">
-        <v>443122.32</v>
+        <v>428626.3</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>443122.32</v>
+        <v>272762.19</v>
       </c>
       <c r="I169" t="n">
-        <v>281986.93</v>
+        <v>428626.3</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>214313.15</v>
       </c>
       <c r="K169" t="n">
-        <v>443122.32</v>
+        <v>214313.15</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Ege Dağıtım ve Ticaret Ltd.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -7062,28 +7062,28 @@
         <v>1200</v>
       </c>
       <c r="F170" t="n">
-        <v>42202.13</v>
+        <v>40821.55</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>42202.13</v>
+        <v>27894.73</v>
       </c>
       <c r="I170" t="n">
-        <v>28838.12</v>
+        <v>40821.55</v>
       </c>
       <c r="J170" t="n">
-        <v>21101.06</v>
+        <v>12246.47</v>
       </c>
       <c r="K170" t="n">
-        <v>21101.06</v>
+        <v>28575.08</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -7101,67 +7101,67 @@
         <v>8900</v>
       </c>
       <c r="F171" t="n">
-        <v>199181.24</v>
+        <v>192665.36</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>199181.24</v>
+        <v>127721.98</v>
       </c>
       <c r="I171" t="n">
-        <v>132041.5</v>
+        <v>192665.36</v>
       </c>
       <c r="J171" t="n">
-        <v>99590.62</v>
+        <v>57799.61</v>
       </c>
       <c r="K171" t="n">
-        <v>99590.62</v>
+        <v>134865.75</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bursa İmalat Tedarik Ltd.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E172" t="n">
-        <v>15400</v>
+        <v>21500</v>
       </c>
       <c r="F172" t="n">
-        <v>1181659.52</v>
+        <v>598406.84</v>
       </c>
       <c r="G172" t="n">
-        <v>94532.75999999999</v>
+        <v>26231.68</v>
       </c>
       <c r="H172" t="n">
-        <v>1087126.76</v>
+        <v>395226.85</v>
       </c>
       <c r="I172" t="n">
-        <v>751965.15</v>
+        <v>572175.16</v>
       </c>
       <c r="J172" t="n">
-        <v>543563.38</v>
+        <v>286087.58</v>
       </c>
       <c r="K172" t="n">
-        <v>543563.38</v>
+        <v>286087.58</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kocaeli Ağır Sanayi Pazarlama</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -7179,106 +7179,106 @@
         <v>15400</v>
       </c>
       <c r="F173" t="n">
-        <v>196943.25</v>
+        <v>190500.58</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>196943.25</v>
+        <v>121227.64</v>
       </c>
       <c r="I173" t="n">
-        <v>125327.52</v>
+        <v>190500.58</v>
       </c>
       <c r="J173" t="n">
-        <v>59082.98</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="K173" t="n">
-        <v>137860.28</v>
+        <v>95250.28999999999</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ürün Delta Kompakt</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E174" t="n">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="F174" t="n">
-        <v>12468.81</v>
+        <v>44532.6</v>
       </c>
       <c r="G174" t="n">
-        <v>374.06</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>12094.75</v>
+        <v>30430.61</v>
       </c>
       <c r="I174" t="n">
-        <v>8440.43</v>
+        <v>44532.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>12094.75</v>
+        <v>44532.6</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ürün Alpha Standart</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E175" t="n">
-        <v>8900</v>
+        <v>1850</v>
       </c>
       <c r="F175" t="n">
-        <v>256090.17</v>
+        <v>131587.65</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>5768.26</v>
       </c>
       <c r="H175" t="n">
-        <v>256090.17</v>
+        <v>88910.58</v>
       </c>
       <c r="I175" t="n">
-        <v>169767.64</v>
+        <v>125819.39</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>62909.69</v>
       </c>
       <c r="K175" t="n">
-        <v>256090.17</v>
+        <v>62909.7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Marmara Perakende Çözümleri</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -7290,73 +7290,73 @@
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>15400</v>
       </c>
       <c r="F176" t="n">
-        <v>1132423.7</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>1132423.7</v>
+        <v>60613.82</v>
       </c>
       <c r="I176" t="n">
-        <v>720633.27</v>
+        <v>95250.28999999999</v>
       </c>
       <c r="J176" t="n">
-        <v>566211.85</v>
+        <v>47625.14</v>
       </c>
       <c r="K176" t="n">
-        <v>566211.85</v>
+        <v>47625.15</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E177" t="n">
-        <v>21500</v>
+        <v>15400</v>
       </c>
       <c r="F177" t="n">
-        <v>274953.24</v>
+        <v>1095378.32</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>274953.24</v>
+        <v>697058.9300000001</v>
       </c>
       <c r="I177" t="n">
-        <v>181597.03</v>
+        <v>1095378.32</v>
       </c>
       <c r="J177" t="n">
-        <v>137476.62</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>137476.62</v>
+        <v>1095378.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>İzmir Ticari Faaliyetler A.Ş.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -7368,145 +7368,145 @@
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E178" t="n">
         <v>21500</v>
       </c>
       <c r="F178" t="n">
-        <v>1099812.97</v>
+        <v>265958.6</v>
       </c>
       <c r="G178" t="n">
-        <v>54990.65</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>1044822.32</v>
+        <v>175656.38</v>
       </c>
       <c r="I178" t="n">
-        <v>726388.1</v>
+        <v>265958.6</v>
       </c>
       <c r="J178" t="n">
-        <v>313446.7</v>
+        <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>731375.63</v>
+        <v>265958.6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ankara Proje Yönetim ve Satış</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ürün Epsilon Profesyonel</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E179" t="n">
-        <v>1850</v>
+        <v>15400</v>
       </c>
       <c r="F179" t="n">
-        <v>53232.23</v>
+        <v>762002.3100000001</v>
       </c>
       <c r="G179" t="n">
-        <v>2661.61</v>
+        <v>20041.82</v>
       </c>
       <c r="H179" t="n">
-        <v>50570.62</v>
+        <v>484910.56</v>
       </c>
       <c r="I179" t="n">
-        <v>35967.72</v>
+        <v>741960.49</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>370980.24</v>
       </c>
       <c r="K179" t="n">
-        <v>50570.62</v>
+        <v>370980.25</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Güneydoğu Pazarlama Ltd.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ürün Zeta Hızlı Tüketim</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E180" t="n">
-        <v>4200</v>
+        <v>650</v>
       </c>
       <c r="F180" t="n">
-        <v>174563.34</v>
+        <v>12060.91</v>
       </c>
       <c r="G180" t="n">
-        <v>8728.17</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>165835.17</v>
+        <v>8164.31</v>
       </c>
       <c r="I180" t="n">
-        <v>116375.56</v>
+        <v>12060.91</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>165835.17</v>
+        <v>12060.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Özel Sipariş Modeli X</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E181" t="n">
-        <v>1850</v>
+        <v>21500</v>
       </c>
       <c r="F181" t="n">
-        <v>29573.46</v>
+        <v>265958.6</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>29573.46</v>
+        <v>175656.38</v>
       </c>
       <c r="I181" t="n">
-        <v>19982.07</v>
+        <v>265958.6</v>
       </c>
       <c r="J181" t="n">
-        <v>14786.73</v>
+        <v>79787.58</v>
       </c>
       <c r="K181" t="n">
-        <v>14786.73</v>
+        <v>186171.02</v>
       </c>
     </row>
   </sheetData>

--- a/demo_data/sectors/uretim_sanayi/sales_ledger.xlsx
+++ b/demo_data/sectors/uretim_sanayi/sales_ledger.xlsx
@@ -492,37 +492,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F2" t="n">
-        <v>20101.6</v>
+        <v>24602.14</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02</v>
+        <v>1555.6</v>
       </c>
       <c r="H2" t="n">
-        <v>13607.18</v>
+        <v>15888.92</v>
       </c>
       <c r="I2" t="n">
-        <v>20101.62</v>
+        <v>23046.54</v>
       </c>
       <c r="J2" t="n">
-        <v>20101.62</v>
+        <v>23046.54</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -531,37 +531,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v>45660</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F3" t="n">
-        <v>70509.95</v>
+        <v>57632.92</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>48181.8</v>
+        <v>36333.8</v>
       </c>
       <c r="I3" t="n">
-        <v>70509.95</v>
+        <v>57632.92</v>
       </c>
       <c r="J3" t="n">
-        <v>70509.95</v>
+        <v>57632.92</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -570,37 +570,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v>45662</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>21500</v>
+        <v>14500</v>
       </c>
       <c r="F4" t="n">
-        <v>199468.95</v>
+        <v>33030.72</v>
       </c>
       <c r="G4" t="n">
-        <v>8743.889999999999</v>
+        <v>835.41</v>
       </c>
       <c r="H4" t="n">
-        <v>131742.28</v>
+        <v>20957.42</v>
       </c>
       <c r="I4" t="n">
-        <v>190725.06</v>
+        <v>32195.31</v>
       </c>
       <c r="J4" t="n">
-        <v>190725.06</v>
+        <v>32195.31</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -609,37 +609,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v>45664</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>8900</v>
       </c>
       <c r="F5" t="n">
-        <v>137618.11</v>
+        <v>30411.05</v>
       </c>
       <c r="G5" t="n">
-        <v>3619.56</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>91229.98</v>
+        <v>20160.13</v>
       </c>
       <c r="I5" t="n">
-        <v>133998.55</v>
+        <v>30411.05</v>
       </c>
       <c r="J5" t="n">
-        <v>133998.55</v>
+        <v>30411.05</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -648,37 +648,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v>45666</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>8900</v>
+        <v>18500</v>
       </c>
       <c r="F6" t="n">
-        <v>247712.6</v>
+        <v>337141.17</v>
       </c>
       <c r="G6" t="n">
-        <v>10858.69</v>
+        <v>12790.35</v>
       </c>
       <c r="H6" t="n">
-        <v>164213.97</v>
+        <v>227798.09</v>
       </c>
       <c r="I6" t="n">
-        <v>236853.91</v>
+        <v>324350.82</v>
       </c>
       <c r="J6" t="n">
-        <v>236853.91</v>
+        <v>324350.82</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -687,37 +687,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v>45668</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>2400</v>
+        <v>18500</v>
       </c>
       <c r="F7" t="n">
-        <v>51954.7</v>
+        <v>189641.91</v>
       </c>
       <c r="G7" t="n">
-        <v>2277.48</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>32471.69</v>
+        <v>128136.43</v>
       </c>
       <c r="I7" t="n">
-        <v>49677.22</v>
+        <v>189641.91</v>
       </c>
       <c r="J7" t="n">
-        <v>49677.22</v>
+        <v>189641.91</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -726,37 +726,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>45670</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F8" t="n">
-        <v>85354.14999999999</v>
+        <v>94308.41</v>
       </c>
       <c r="G8" t="n">
-        <v>1496.63</v>
+        <v>5963.07</v>
       </c>
       <c r="H8" t="n">
-        <v>58325.34</v>
+        <v>59455.3</v>
       </c>
       <c r="I8" t="n">
-        <v>83857.52</v>
+        <v>88345.34</v>
       </c>
       <c r="J8" t="n">
-        <v>83857.52</v>
+        <v>88345.34</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -765,37 +765,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>650</v>
+        <v>4600</v>
       </c>
       <c r="F9" t="n">
-        <v>30152.28</v>
+        <v>99547.77</v>
       </c>
       <c r="G9" t="n">
-        <v>1321.75</v>
+        <v>3776.61</v>
       </c>
       <c r="H9" t="n">
-        <v>20410.78</v>
+        <v>62758.37</v>
       </c>
       <c r="I9" t="n">
-        <v>28830.53</v>
+        <v>95771.16</v>
       </c>
       <c r="J9" t="n">
-        <v>28830.53</v>
+        <v>95771.16</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -804,12 +804,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -819,22 +819,22 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F10" t="n">
-        <v>103909.41</v>
+        <v>81096.12</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>69272.94</v>
+        <v>53760.35</v>
       </c>
       <c r="I10" t="n">
-        <v>103909.41</v>
+        <v>81096.12</v>
       </c>
       <c r="J10" t="n">
-        <v>103909.41</v>
+        <v>81096.12</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -843,37 +843,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v>45676</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F11" t="n">
-        <v>2010.15</v>
+        <v>87702.25999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>88.12</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1360.72</v>
+        <v>59227.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1922.03</v>
+        <v>87702.25999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>1922.03</v>
+        <v>87702.25999999999</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -882,37 +882,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v>45678</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F12" t="n">
-        <v>70509.95</v>
+        <v>31436.14</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1192.61</v>
       </c>
       <c r="H12" t="n">
-        <v>48181.8</v>
+        <v>19818.43</v>
       </c>
       <c r="I12" t="n">
-        <v>70509.95</v>
+        <v>30243.53</v>
       </c>
       <c r="J12" t="n">
-        <v>70509.95</v>
+        <v>30243.53</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -921,37 +921,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v>45680</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F13" t="n">
-        <v>298739.54</v>
+        <v>35536.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2246.95</v>
       </c>
       <c r="H13" t="n">
-        <v>199159.69</v>
+        <v>22950.66</v>
       </c>
       <c r="I13" t="n">
-        <v>298739.54</v>
+        <v>33289.55</v>
       </c>
       <c r="J13" t="n">
-        <v>298739.54</v>
+        <v>33289.55</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -960,37 +960,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v>45682</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>4200</v>
+        <v>95000</v>
       </c>
       <c r="F14" t="n">
-        <v>25977.35</v>
+        <v>973836.83</v>
       </c>
       <c r="G14" t="n">
-        <v>455.5</v>
+        <v>61575.18</v>
       </c>
       <c r="H14" t="n">
-        <v>17318.23</v>
+        <v>697062.16</v>
       </c>
       <c r="I14" t="n">
-        <v>25521.85</v>
+        <v>912261.65</v>
       </c>
       <c r="J14" t="n">
-        <v>25521.85</v>
+        <v>912261.65</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -999,37 +999,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v>45684</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F15" t="n">
-        <v>33399.45</v>
+        <v>20957.42</v>
       </c>
       <c r="G15" t="n">
-        <v>878.46</v>
+        <v>1325.13</v>
       </c>
       <c r="H15" t="n">
-        <v>22822.96</v>
+        <v>13212.29</v>
       </c>
       <c r="I15" t="n">
-        <v>32520.99</v>
+        <v>19632.29</v>
       </c>
       <c r="J15" t="n">
-        <v>32520.99</v>
+        <v>19632.29</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1038,37 +1038,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v>45686</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>8900</v>
+        <v>14500</v>
       </c>
       <c r="F16" t="n">
-        <v>660566.9300000001</v>
+        <v>181668.98</v>
       </c>
       <c r="G16" t="n">
-        <v>28956.52</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>437903.92</v>
+        <v>115265.83</v>
       </c>
       <c r="I16" t="n">
-        <v>631610.41</v>
+        <v>181668.98</v>
       </c>
       <c r="J16" t="n">
-        <v>631610.41</v>
+        <v>181668.98</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1077,37 +1077,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F17" t="n">
-        <v>531917.1899999999</v>
+        <v>16401.46</v>
       </c>
       <c r="G17" t="n">
-        <v>13990.23</v>
+        <v>622.23</v>
       </c>
       <c r="H17" t="n">
-        <v>351312.75</v>
+        <v>10592.61</v>
       </c>
       <c r="I17" t="n">
-        <v>517926.96</v>
+        <v>15779.23</v>
       </c>
       <c r="J17" t="n">
-        <v>517926.96</v>
+        <v>15779.23</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1116,37 +1116,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v>45690</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F18" t="n">
-        <v>51954.7</v>
+        <v>47154.2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2981.54</v>
       </c>
       <c r="H18" t="n">
-        <v>32471.69</v>
+        <v>29727.65</v>
       </c>
       <c r="I18" t="n">
-        <v>51954.7</v>
+        <v>44172.66</v>
       </c>
       <c r="J18" t="n">
-        <v>51954.7</v>
+        <v>44172.66</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1155,37 +1155,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v>45692</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>2400</v>
+        <v>95000</v>
       </c>
       <c r="F19" t="n">
-        <v>89065.2</v>
+        <v>432816.37</v>
       </c>
       <c r="G19" t="n">
-        <v>2342.55</v>
+        <v>10946.7</v>
       </c>
       <c r="H19" t="n">
-        <v>55665.75</v>
+        <v>309805.4</v>
       </c>
       <c r="I19" t="n">
-        <v>86722.64999999999</v>
+        <v>421869.67</v>
       </c>
       <c r="J19" t="n">
-        <v>86722.64999999999</v>
+        <v>421869.67</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1194,37 +1194,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>21500</v>
+        <v>18500</v>
       </c>
       <c r="F20" t="n">
-        <v>1595751.58</v>
+        <v>252855.88</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1053938.26</v>
+        <v>170848.57</v>
       </c>
       <c r="I20" t="n">
-        <v>1595751.58</v>
+        <v>252855.88</v>
       </c>
       <c r="J20" t="n">
-        <v>1595751.58</v>
+        <v>252855.88</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1233,37 +1233,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>4200</v>
+        <v>95000</v>
       </c>
       <c r="F21" t="n">
-        <v>25977.35</v>
+        <v>1190245.02</v>
       </c>
       <c r="G21" t="n">
-        <v>683.24</v>
+        <v>45155.14</v>
       </c>
       <c r="H21" t="n">
-        <v>17318.23</v>
+        <v>851964.86</v>
       </c>
       <c r="I21" t="n">
-        <v>25294.11</v>
+        <v>1145089.88</v>
       </c>
       <c r="J21" t="n">
-        <v>25294.11</v>
+        <v>1145089.88</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1272,37 +1272,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>45698</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F22" t="n">
-        <v>8040.61</v>
+        <v>526213.59</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>13308.88</v>
       </c>
       <c r="H22" t="n">
-        <v>5442.87</v>
+        <v>355365.02</v>
       </c>
       <c r="I22" t="n">
-        <v>8040.61</v>
+        <v>512904.71</v>
       </c>
       <c r="J22" t="n">
-        <v>8040.61</v>
+        <v>512904.71</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1311,37 +1311,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>1200</v>
+        <v>38500</v>
       </c>
       <c r="F23" t="n">
-        <v>66798.89999999999</v>
+        <v>350809.06</v>
       </c>
       <c r="G23" t="n">
-        <v>1756.91</v>
+        <v>22181.47</v>
       </c>
       <c r="H23" t="n">
-        <v>45645.92</v>
+        <v>236910.01</v>
       </c>
       <c r="I23" t="n">
-        <v>65041.99</v>
+        <v>328627.59</v>
       </c>
       <c r="J23" t="n">
-        <v>65041.99</v>
+        <v>328627.59</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1350,37 +1350,37 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>45702</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>2400</v>
+        <v>38500</v>
       </c>
       <c r="F24" t="n">
-        <v>44532.6</v>
+        <v>701618.12</v>
       </c>
       <c r="G24" t="n">
-        <v>780.85</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>27832.88</v>
+        <v>473820.03</v>
       </c>
       <c r="I24" t="n">
-        <v>43751.75</v>
+        <v>701618.12</v>
       </c>
       <c r="J24" t="n">
-        <v>43751.75</v>
+        <v>701618.12</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1389,37 +1389,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>45704</v>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="F25" t="n">
-        <v>11133.15</v>
+        <v>337141.17</v>
       </c>
       <c r="G25" t="n">
-        <v>292.82</v>
+        <v>21317.26</v>
       </c>
       <c r="H25" t="n">
-        <v>7607.65</v>
+        <v>227798.09</v>
       </c>
       <c r="I25" t="n">
-        <v>10840.33</v>
+        <v>315823.91</v>
       </c>
       <c r="J25" t="n">
-        <v>10840.33</v>
+        <v>315823.91</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1428,37 +1428,37 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F26" t="n">
-        <v>25977.35</v>
+        <v>172329.26</v>
       </c>
       <c r="G26" t="n">
-        <v>1138.74</v>
+        <v>10896.29</v>
       </c>
       <c r="H26" t="n">
-        <v>17318.23</v>
+        <v>114240.74</v>
       </c>
       <c r="I26" t="n">
-        <v>24838.61</v>
+        <v>161432.97</v>
       </c>
       <c r="J26" t="n">
-        <v>24838.61</v>
+        <v>161432.97</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1467,37 +1467,37 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>1850</v>
+        <v>18500</v>
       </c>
       <c r="F27" t="n">
-        <v>17163.61</v>
+        <v>379283.82</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>11597.03</v>
+        <v>256272.85</v>
       </c>
       <c r="I27" t="n">
-        <v>17163.61</v>
+        <v>379283.82</v>
       </c>
       <c r="J27" t="n">
-        <v>17163.61</v>
+        <v>379283.82</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1506,37 +1506,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>45710</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
         <v>2400</v>
       </c>
       <c r="F28" t="n">
-        <v>118753.61</v>
+        <v>32802.92</v>
       </c>
       <c r="G28" t="n">
-        <v>3123.4</v>
+        <v>1244.47</v>
       </c>
       <c r="H28" t="n">
-        <v>74221</v>
+        <v>21185.22</v>
       </c>
       <c r="I28" t="n">
-        <v>115630.21</v>
+        <v>31558.45</v>
       </c>
       <c r="J28" t="n">
-        <v>115630.21</v>
+        <v>31558.45</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1545,37 +1545,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>45712</v>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>2400</v>
+        <v>38500</v>
       </c>
       <c r="F29" t="n">
-        <v>14844.2</v>
+        <v>350809.06</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>9277.629999999999</v>
+        <v>236910.01</v>
       </c>
       <c r="I29" t="n">
-        <v>14844.2</v>
+        <v>350809.06</v>
       </c>
       <c r="J29" t="n">
-        <v>14844.2</v>
+        <v>350809.06</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1584,37 +1584,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F30" t="n">
-        <v>74375.63</v>
+        <v>10137.02</v>
       </c>
       <c r="G30" t="n">
-        <v>1304.13</v>
+        <v>640.96</v>
       </c>
       <c r="H30" t="n">
-        <v>50253.8</v>
+        <v>6720.04</v>
       </c>
       <c r="I30" t="n">
-        <v>73071.5</v>
+        <v>9496.059999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>73071.5</v>
+        <v>9496.059999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1623,37 +1623,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F31" t="n">
-        <v>664896.49</v>
+        <v>865632.74</v>
       </c>
       <c r="G31" t="n">
-        <v>17487.79</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>439140.94</v>
+        <v>619610.8</v>
       </c>
       <c r="I31" t="n">
-        <v>647408.7</v>
+        <v>865632.74</v>
       </c>
       <c r="J31" t="n">
-        <v>647408.7</v>
+        <v>865632.74</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1662,37 +1662,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>45718</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>21500</v>
+        <v>4600</v>
       </c>
       <c r="F32" t="n">
-        <v>332448.25</v>
+        <v>10478.71</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>219570.47</v>
+        <v>6606.14</v>
       </c>
       <c r="I32" t="n">
-        <v>332448.25</v>
+        <v>10478.71</v>
       </c>
       <c r="J32" t="n">
-        <v>332448.25</v>
+        <v>10478.71</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1701,37 +1701,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>45720</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>1200</v>
+        <v>38500</v>
       </c>
       <c r="F33" t="n">
-        <v>7422.1</v>
+        <v>482362.46</v>
       </c>
       <c r="G33" t="n">
-        <v>325.35</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>5071.77</v>
+        <v>325751.27</v>
       </c>
       <c r="I33" t="n">
-        <v>7096.75</v>
+        <v>482362.46</v>
       </c>
       <c r="J33" t="n">
-        <v>7096.75</v>
+        <v>482362.46</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1740,37 +1740,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v>45722</v>
       </c>
       <c r="D34" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F34" t="n">
-        <v>137308.86</v>
+        <v>162192.24</v>
       </c>
       <c r="G34" t="n">
-        <v>2407.62</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>92776.25</v>
+        <v>107520.7</v>
       </c>
       <c r="I34" t="n">
-        <v>134901.24</v>
+        <v>162192.24</v>
       </c>
       <c r="J34" t="n">
-        <v>134901.24</v>
+        <v>162192.24</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -1779,12 +1779,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
@@ -1794,22 +1794,22 @@
         <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>1850</v>
+        <v>4600</v>
       </c>
       <c r="F35" t="n">
-        <v>108702.85</v>
+        <v>99547.77</v>
       </c>
       <c r="G35" t="n">
-        <v>2859.05</v>
+        <v>6294.35</v>
       </c>
       <c r="H35" t="n">
-        <v>73447.87</v>
+        <v>62758.37</v>
       </c>
       <c r="I35" t="n">
-        <v>105843.8</v>
+        <v>93253.42</v>
       </c>
       <c r="J35" t="n">
-        <v>105843.8</v>
+        <v>93253.42</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1818,37 +1818,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v>45726</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>8900</v>
+        <v>18500</v>
       </c>
       <c r="F36" t="n">
-        <v>55047.24</v>
+        <v>337141.17</v>
       </c>
       <c r="G36" t="n">
-        <v>2413.04</v>
+        <v>12790.35</v>
       </c>
       <c r="H36" t="n">
-        <v>36491.99</v>
+        <v>227798.09</v>
       </c>
       <c r="I36" t="n">
-        <v>52634.2</v>
+        <v>324350.82</v>
       </c>
       <c r="J36" t="n">
-        <v>52634.2</v>
+        <v>324350.82</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1857,37 +1857,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" t="n">
-        <v>8900</v>
+        <v>38500</v>
       </c>
       <c r="F37" t="n">
-        <v>82570.87</v>
+        <v>175404.53</v>
       </c>
       <c r="G37" t="n">
-        <v>3619.56</v>
+        <v>6654.44</v>
       </c>
       <c r="H37" t="n">
-        <v>54737.99</v>
+        <v>118455.01</v>
       </c>
       <c r="I37" t="n">
-        <v>78951.31</v>
+        <v>168750.09</v>
       </c>
       <c r="J37" t="n">
-        <v>78951.31</v>
+        <v>168750.09</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1896,37 +1896,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v>45730</v>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E38" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F38" t="n">
-        <v>48243.65</v>
+        <v>38270.08</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1451.88</v>
       </c>
       <c r="H38" t="n">
-        <v>32966.5</v>
+        <v>24716.09</v>
       </c>
       <c r="I38" t="n">
-        <v>48243.65</v>
+        <v>36818.2</v>
       </c>
       <c r="J38" t="n">
-        <v>48243.65</v>
+        <v>36818.2</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1935,37 +1935,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v>45732</v>
       </c>
       <c r="D39" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F39" t="n">
-        <v>70509.95</v>
+        <v>20957.42</v>
       </c>
       <c r="G39" t="n">
-        <v>3090.86</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>48181.8</v>
+        <v>13212.29</v>
       </c>
       <c r="I39" t="n">
-        <v>67419.09</v>
+        <v>20957.42</v>
       </c>
       <c r="J39" t="n">
-        <v>67419.09</v>
+        <v>20957.42</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -1974,37 +1974,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v>45734</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="F40" t="n">
-        <v>181841.46</v>
+        <v>57632.92</v>
       </c>
       <c r="G40" t="n">
-        <v>7971.18</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>121227.64</v>
+        <v>36333.8</v>
       </c>
       <c r="I40" t="n">
-        <v>173870.28</v>
+        <v>57632.92</v>
       </c>
       <c r="J40" t="n">
-        <v>173870.28</v>
+        <v>57632.92</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2013,37 +2013,37 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>45736</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>650</v>
+        <v>18500</v>
       </c>
       <c r="F41" t="n">
-        <v>18091.37</v>
+        <v>147499.26</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>9326.299999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>12246.47</v>
+        <v>99661.66</v>
       </c>
       <c r="I41" t="n">
-        <v>18091.37</v>
+        <v>138172.96</v>
       </c>
       <c r="J41" t="n">
-        <v>18091.37</v>
+        <v>138172.96</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2052,37 +2052,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v>45738</v>
       </c>
       <c r="D42" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>650</v>
+        <v>18500</v>
       </c>
       <c r="F42" t="n">
-        <v>16081.22</v>
+        <v>294998.53</v>
       </c>
       <c r="G42" t="n">
-        <v>281.97</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>10885.75</v>
+        <v>199323.33</v>
       </c>
       <c r="I42" t="n">
-        <v>15799.25</v>
+        <v>294998.53</v>
       </c>
       <c r="J42" t="n">
-        <v>15799.25</v>
+        <v>294998.53</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2091,37 +2091,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v>45740</v>
       </c>
       <c r="D43" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E43" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F43" t="n">
-        <v>605519.6899999999</v>
+        <v>21868.62</v>
       </c>
       <c r="G43" t="n">
-        <v>10617.39</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>401411.93</v>
+        <v>14123.48</v>
       </c>
       <c r="I43" t="n">
-        <v>594902.3</v>
+        <v>21868.62</v>
       </c>
       <c r="J43" t="n">
-        <v>594902.3</v>
+        <v>21868.62</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2130,37 +2130,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>650</v>
+        <v>14500</v>
       </c>
       <c r="F44" t="n">
-        <v>50253.8</v>
+        <v>297276.51</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>34017.96</v>
+        <v>188616.82</v>
       </c>
       <c r="I44" t="n">
-        <v>50253.8</v>
+        <v>297276.51</v>
       </c>
       <c r="J44" t="n">
-        <v>50253.8</v>
+        <v>297276.51</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2169,37 +2169,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v>45744</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>21500</v>
+        <v>4600</v>
       </c>
       <c r="F45" t="n">
-        <v>1329792.99</v>
+        <v>94308.41</v>
       </c>
       <c r="G45" t="n">
-        <v>58292.62</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>878281.88</v>
+        <v>59455.3</v>
       </c>
       <c r="I45" t="n">
-        <v>1271500.37</v>
+        <v>94308.41</v>
       </c>
       <c r="J45" t="n">
-        <v>1271500.37</v>
+        <v>94308.41</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2208,37 +2208,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>45746</v>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>4200</v>
+        <v>14500</v>
       </c>
       <c r="F46" t="n">
-        <v>233796.16</v>
+        <v>132122.89</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>155864.11</v>
+        <v>83829.7</v>
       </c>
       <c r="I46" t="n">
-        <v>233796.16</v>
+        <v>132122.89</v>
       </c>
       <c r="J46" t="n">
-        <v>233796.16</v>
+        <v>132122.89</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2247,37 +2247,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v>45749</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F47" t="n">
-        <v>238125.72</v>
+        <v>43737.23</v>
       </c>
       <c r="G47" t="n">
-        <v>4175.38</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>151534.55</v>
+        <v>28246.96</v>
       </c>
       <c r="I47" t="n">
-        <v>233950.34</v>
+        <v>43737.23</v>
       </c>
       <c r="J47" t="n">
-        <v>233950.34</v>
+        <v>43737.23</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2286,37 +2286,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>45751</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>4200</v>
+        <v>38500</v>
       </c>
       <c r="F48" t="n">
-        <v>103909.41</v>
+        <v>263106.79</v>
       </c>
       <c r="G48" t="n">
-        <v>1821.98</v>
+        <v>9981.66</v>
       </c>
       <c r="H48" t="n">
-        <v>69272.94</v>
+        <v>177682.51</v>
       </c>
       <c r="I48" t="n">
-        <v>102087.43</v>
+        <v>253125.13</v>
       </c>
       <c r="J48" t="n">
-        <v>102087.43</v>
+        <v>253125.13</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2325,37 +2325,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v>45753</v>
       </c>
       <c r="D49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
-        <v>8900</v>
+        <v>2400</v>
       </c>
       <c r="F49" t="n">
-        <v>412854.33</v>
+        <v>24602.19</v>
       </c>
       <c r="G49" t="n">
-        <v>18097.82</v>
+        <v>933.35</v>
       </c>
       <c r="H49" t="n">
-        <v>273689.95</v>
+        <v>15888.92</v>
       </c>
       <c r="I49" t="n">
-        <v>394756.51</v>
+        <v>23668.84</v>
       </c>
       <c r="J49" t="n">
-        <v>394756.51</v>
+        <v>23668.84</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2364,37 +2364,37 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v>45755</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F50" t="n">
-        <v>952502.88</v>
+        <v>49204.39</v>
       </c>
       <c r="G50" t="n">
-        <v>41753.78</v>
+        <v>1866.7</v>
       </c>
       <c r="H50" t="n">
-        <v>606138.2</v>
+        <v>31777.83</v>
       </c>
       <c r="I50" t="n">
-        <v>910749.1</v>
+        <v>47337.69</v>
       </c>
       <c r="J50" t="n">
-        <v>910749.1</v>
+        <v>47337.69</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2403,37 +2403,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="F51" t="n">
-        <v>1047753.17</v>
+        <v>210713.23</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>666752.02</v>
+        <v>142373.81</v>
       </c>
       <c r="I51" t="n">
-        <v>1047753.17</v>
+        <v>210713.23</v>
       </c>
       <c r="J51" t="n">
-        <v>1047753.17</v>
+        <v>210713.23</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2442,37 +2442,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v>45759</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>8900</v>
+        <v>95000</v>
       </c>
       <c r="F52" t="n">
-        <v>247712.6</v>
+        <v>1947673.67</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>164213.97</v>
+        <v>1394124.31</v>
       </c>
       <c r="I52" t="n">
-        <v>247712.6</v>
+        <v>1947673.67</v>
       </c>
       <c r="J52" t="n">
-        <v>247712.6</v>
+        <v>1947673.67</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2481,37 +2481,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v>45761</v>
       </c>
       <c r="D53" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>4200</v>
+        <v>38500</v>
       </c>
       <c r="F53" t="n">
-        <v>311728.22</v>
+        <v>87702.25999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>13664.87</v>
+        <v>5545.37</v>
       </c>
       <c r="H53" t="n">
-        <v>207818.81</v>
+        <v>59227.5</v>
       </c>
       <c r="I53" t="n">
-        <v>298063.35</v>
+        <v>82156.89</v>
       </c>
       <c r="J53" t="n">
-        <v>298063.35</v>
+        <v>82156.89</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2520,37 +2520,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>45763</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>15400</v>
+        <v>95000</v>
       </c>
       <c r="F54" t="n">
-        <v>476251.44</v>
+        <v>1839469.58</v>
       </c>
       <c r="G54" t="n">
-        <v>20876.89</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>303069.1</v>
+        <v>1316672.96</v>
       </c>
       <c r="I54" t="n">
-        <v>455374.55</v>
+        <v>1839469.58</v>
       </c>
       <c r="J54" t="n">
-        <v>455374.55</v>
+        <v>1839469.58</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2559,37 +2559,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v>45765</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>650</v>
+        <v>95000</v>
       </c>
       <c r="F55" t="n">
-        <v>14071.07</v>
+        <v>324612.28</v>
       </c>
       <c r="G55" t="n">
-        <v>246.73</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>9525.030000000001</v>
+        <v>232354.05</v>
       </c>
       <c r="I55" t="n">
-        <v>13824.34</v>
+        <v>324612.28</v>
       </c>
       <c r="J55" t="n">
-        <v>13824.34</v>
+        <v>324612.28</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2598,37 +2598,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>45767</v>
       </c>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F56" t="n">
-        <v>598406.84</v>
+        <v>324612.28</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>395226.85</v>
+        <v>232354.05</v>
       </c>
       <c r="I56" t="n">
-        <v>598406.84</v>
+        <v>324612.28</v>
       </c>
       <c r="J56" t="n">
-        <v>598406.84</v>
+        <v>324612.28</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2637,37 +2637,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>45769</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E57" t="n">
-        <v>2400</v>
+        <v>38500</v>
       </c>
       <c r="F57" t="n">
-        <v>66798.89999999999</v>
+        <v>833171.51</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>41749.31</v>
+        <v>562661.28</v>
       </c>
       <c r="I57" t="n">
-        <v>66798.89999999999</v>
+        <v>833171.51</v>
       </c>
       <c r="J57" t="n">
-        <v>66798.89999999999</v>
+        <v>833171.51</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2676,37 +2676,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D58" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>650</v>
+        <v>95000</v>
       </c>
       <c r="F58" t="n">
-        <v>50253.8</v>
+        <v>324612.28</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>12315.04</v>
       </c>
       <c r="H58" t="n">
-        <v>34017.96</v>
+        <v>232354.05</v>
       </c>
       <c r="I58" t="n">
-        <v>50253.8</v>
+        <v>312297.24</v>
       </c>
       <c r="J58" t="n">
-        <v>50253.8</v>
+        <v>312297.24</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2715,37 +2715,37 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="D59" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E59" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F59" t="n">
-        <v>285750.87</v>
+        <v>70959.11</v>
       </c>
       <c r="G59" t="n">
-        <v>7515.68</v>
+        <v>1794.68</v>
       </c>
       <c r="H59" t="n">
-        <v>181841.46</v>
+        <v>47040.31</v>
       </c>
       <c r="I59" t="n">
-        <v>278235.19</v>
+        <v>69164.42999999999</v>
       </c>
       <c r="J59" t="n">
-        <v>278235.19</v>
+        <v>69164.42999999999</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2754,37 +2754,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>45775</v>
       </c>
       <c r="D60" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E60" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F60" t="n">
-        <v>133597.81</v>
+        <v>131781.2</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>83498.63</v>
+        <v>87360.57000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>133597.81</v>
+        <v>131781.2</v>
       </c>
       <c r="J60" t="n">
-        <v>133597.81</v>
+        <v>131781.2</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2793,37 +2793,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E61" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F61" t="n">
-        <v>298739.54</v>
+        <v>30069.35</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>199159.69</v>
+        <v>19419.79</v>
       </c>
       <c r="I61" t="n">
-        <v>298739.54</v>
+        <v>30069.35</v>
       </c>
       <c r="J61" t="n">
-        <v>298739.54</v>
+        <v>30069.35</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2832,37 +2832,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D62" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F62" t="n">
-        <v>68654.42999999999</v>
+        <v>54671.54</v>
       </c>
       <c r="G62" t="n">
-        <v>3009.53</v>
+        <v>3456.85</v>
       </c>
       <c r="H62" t="n">
-        <v>46388.13</v>
+        <v>35308.7</v>
       </c>
       <c r="I62" t="n">
-        <v>65644.89999999999</v>
+        <v>51214.69</v>
       </c>
       <c r="J62" t="n">
-        <v>65644.89999999999</v>
+        <v>51214.69</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -2871,37 +2871,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v>45781</v>
       </c>
       <c r="D63" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>8900</v>
+        <v>38500</v>
       </c>
       <c r="F63" t="n">
-        <v>385330.71</v>
+        <v>789320.38</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>255443.96</v>
+        <v>533047.53</v>
       </c>
       <c r="I63" t="n">
-        <v>385330.71</v>
+        <v>789320.38</v>
       </c>
       <c r="J63" t="n">
-        <v>385330.71</v>
+        <v>789320.38</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2910,12 +2910,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
@@ -2925,22 +2925,22 @@
         <v>12</v>
       </c>
       <c r="E64" t="n">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="F64" t="n">
-        <v>571501.73</v>
+        <v>252855.88</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>363682.92</v>
+        <v>170848.57</v>
       </c>
       <c r="I64" t="n">
-        <v>571501.73</v>
+        <v>252855.88</v>
       </c>
       <c r="J64" t="n">
-        <v>571501.73</v>
+        <v>252855.88</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2949,37 +2949,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v>45785</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E65" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F65" t="n">
-        <v>14071.07</v>
+        <v>101370.15</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>9525.030000000001</v>
+        <v>67200.44</v>
       </c>
       <c r="I65" t="n">
-        <v>14071.07</v>
+        <v>101370.15</v>
       </c>
       <c r="J65" t="n">
-        <v>14071.07</v>
+        <v>101370.15</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2988,37 +2988,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v>45787</v>
       </c>
       <c r="D66" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E66" t="n">
-        <v>4200</v>
+        <v>14500</v>
       </c>
       <c r="F66" t="n">
-        <v>155864.11</v>
+        <v>297276.51</v>
       </c>
       <c r="G66" t="n">
-        <v>6832.44</v>
+        <v>7518.65</v>
       </c>
       <c r="H66" t="n">
-        <v>103909.41</v>
+        <v>188616.82</v>
       </c>
       <c r="I66" t="n">
-        <v>149031.67</v>
+        <v>289757.86</v>
       </c>
       <c r="J66" t="n">
-        <v>149031.67</v>
+        <v>289757.86</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -3027,37 +3027,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E67" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F67" t="n">
-        <v>148442.01</v>
+        <v>94308.41</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2385.23</v>
       </c>
       <c r="H67" t="n">
-        <v>92776.25</v>
+        <v>59455.3</v>
       </c>
       <c r="I67" t="n">
-        <v>148442.01</v>
+        <v>91923.17999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>148442.01</v>
+        <v>91923.17999999999</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3066,37 +3066,37 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v>45791</v>
       </c>
       <c r="D68" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E68" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="F68" t="n">
-        <v>22266.3</v>
+        <v>189641.91</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>15215.31</v>
+        <v>128136.43</v>
       </c>
       <c r="I68" t="n">
-        <v>22266.3</v>
+        <v>189641.91</v>
       </c>
       <c r="J68" t="n">
-        <v>22266.3</v>
+        <v>189641.91</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3105,37 +3105,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>45793</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E69" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F69" t="n">
-        <v>7422.1</v>
+        <v>94308.41</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>4638.81</v>
+        <v>59455.3</v>
       </c>
       <c r="I69" t="n">
-        <v>7422.1</v>
+        <v>94308.41</v>
       </c>
       <c r="J69" t="n">
-        <v>7422.1</v>
+        <v>94308.41</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3144,37 +3144,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>45795</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E70" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F70" t="n">
-        <v>28142.13</v>
+        <v>202740.3</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>19050.06</v>
+        <v>134400.87</v>
       </c>
       <c r="I70" t="n">
-        <v>28142.13</v>
+        <v>202740.3</v>
       </c>
       <c r="J70" t="n">
-        <v>28142.13</v>
+        <v>202740.3</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -3183,37 +3183,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>45797</v>
       </c>
       <c r="D71" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E71" t="n">
-        <v>8900</v>
+        <v>18500</v>
       </c>
       <c r="F71" t="n">
-        <v>633043.3100000001</v>
+        <v>189641.91</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>11990.96</v>
       </c>
       <c r="H71" t="n">
-        <v>419657.93</v>
+        <v>128136.43</v>
       </c>
       <c r="I71" t="n">
-        <v>633043.3100000001</v>
+        <v>177650.95</v>
       </c>
       <c r="J71" t="n">
-        <v>633043.3100000001</v>
+        <v>177650.95</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3222,37 +3222,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D72" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F72" t="n">
-        <v>91539.24000000001</v>
+        <v>20274.03</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>61850.84</v>
+        <v>13440.09</v>
       </c>
       <c r="I72" t="n">
-        <v>91539.24000000001</v>
+        <v>20274.03</v>
       </c>
       <c r="J72" t="n">
-        <v>91539.24000000001</v>
+        <v>20274.03</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3261,37 +3261,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v>45801</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E73" t="n">
-        <v>21500</v>
+        <v>14500</v>
       </c>
       <c r="F73" t="n">
-        <v>797875.79</v>
+        <v>148638.25</v>
       </c>
       <c r="G73" t="n">
-        <v>13990.23</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>526969.13</v>
+        <v>94308.41</v>
       </c>
       <c r="I73" t="n">
-        <v>783885.5600000001</v>
+        <v>148638.25</v>
       </c>
       <c r="J73" t="n">
-        <v>783885.5600000001</v>
+        <v>148638.25</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3300,37 +3300,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v>45803</v>
       </c>
       <c r="D74" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F74" t="n">
-        <v>29688.4</v>
+        <v>50685.08</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1281.92</v>
       </c>
       <c r="H74" t="n">
-        <v>20287.07</v>
+        <v>33600.22</v>
       </c>
       <c r="I74" t="n">
-        <v>29688.4</v>
+        <v>49403.16</v>
       </c>
       <c r="J74" t="n">
-        <v>29688.4</v>
+        <v>49403.16</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -3339,37 +3339,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v>45805</v>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E75" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F75" t="n">
-        <v>48243.65</v>
+        <v>78590.34</v>
       </c>
       <c r="G75" t="n">
-        <v>845.92</v>
+        <v>4969.23</v>
       </c>
       <c r="H75" t="n">
-        <v>32966.5</v>
+        <v>49546.08</v>
       </c>
       <c r="I75" t="n">
-        <v>47397.73</v>
+        <v>73621.11</v>
       </c>
       <c r="J75" t="n">
-        <v>47397.73</v>
+        <v>73621.11</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3378,37 +3378,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v>45807</v>
       </c>
       <c r="D76" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>4200</v>
+        <v>95000</v>
       </c>
       <c r="F76" t="n">
-        <v>324716.89</v>
+        <v>108204.09</v>
       </c>
       <c r="G76" t="n">
-        <v>5693.7</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>216477.93</v>
+        <v>77451.35000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>319023.19</v>
+        <v>108204.09</v>
       </c>
       <c r="J76" t="n">
-        <v>319023.19</v>
+        <v>108204.09</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3417,37 +3417,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F77" t="n">
-        <v>163286.21</v>
+        <v>26196.78</v>
       </c>
       <c r="G77" t="n">
-        <v>7157.79</v>
+        <v>1656.41</v>
       </c>
       <c r="H77" t="n">
-        <v>102053.88</v>
+        <v>16515.36</v>
       </c>
       <c r="I77" t="n">
-        <v>156128.42</v>
+        <v>24540.37</v>
       </c>
       <c r="J77" t="n">
-        <v>156128.42</v>
+        <v>24540.37</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3456,37 +3456,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v>45811</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E78" t="n">
-        <v>1850</v>
+        <v>14500</v>
       </c>
       <c r="F78" t="n">
-        <v>22884.81</v>
+        <v>198184.34</v>
       </c>
       <c r="G78" t="n">
-        <v>401.27</v>
+        <v>12531.09</v>
       </c>
       <c r="H78" t="n">
-        <v>15462.71</v>
+        <v>125744.55</v>
       </c>
       <c r="I78" t="n">
-        <v>22483.54</v>
+        <v>185653.25</v>
       </c>
       <c r="J78" t="n">
-        <v>22483.54</v>
+        <v>185653.25</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
@@ -3495,37 +3495,37 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E79" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F79" t="n">
-        <v>95250.28999999999</v>
+        <v>13667.89</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>60613.82</v>
+        <v>8827.18</v>
       </c>
       <c r="I79" t="n">
-        <v>95250.28999999999</v>
+        <v>13667.89</v>
       </c>
       <c r="J79" t="n">
-        <v>95250.28999999999</v>
+        <v>13667.89</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -3534,37 +3534,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>45815</v>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F80" t="n">
-        <v>89065.2</v>
+        <v>20274.03</v>
       </c>
       <c r="G80" t="n">
-        <v>1561.7</v>
+        <v>512.77</v>
       </c>
       <c r="H80" t="n">
-        <v>55665.75</v>
+        <v>13440.09</v>
       </c>
       <c r="I80" t="n">
-        <v>87503.5</v>
+        <v>19761.26</v>
       </c>
       <c r="J80" t="n">
-        <v>87503.5</v>
+        <v>19761.26</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3573,37 +3573,37 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v>45817</v>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E81" t="n">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="F81" t="n">
-        <v>168852.78</v>
+        <v>41914.85</v>
       </c>
       <c r="G81" t="n">
-        <v>7401.81</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>112568.52</v>
+        <v>26424.58</v>
       </c>
       <c r="I81" t="n">
-        <v>161450.97</v>
+        <v>41914.85</v>
       </c>
       <c r="J81" t="n">
-        <v>161450.97</v>
+        <v>41914.85</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3612,37 +3612,37 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E82" t="n">
-        <v>15400</v>
+        <v>14500</v>
       </c>
       <c r="F82" t="n">
-        <v>95250.28999999999</v>
+        <v>297276.51</v>
       </c>
       <c r="G82" t="n">
-        <v>2505.23</v>
+        <v>11277.98</v>
       </c>
       <c r="H82" t="n">
-        <v>60613.82</v>
+        <v>188616.82</v>
       </c>
       <c r="I82" t="n">
-        <v>92745.06</v>
+        <v>285998.53</v>
       </c>
       <c r="J82" t="n">
-        <v>92745.06</v>
+        <v>285998.53</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3651,37 +3651,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>45821</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="F83" t="n">
-        <v>44532.6</v>
+        <v>126427.94</v>
       </c>
       <c r="G83" t="n">
-        <v>1171.27</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>30430.61</v>
+        <v>85424.28</v>
       </c>
       <c r="I83" t="n">
-        <v>43361.33</v>
+        <v>126427.94</v>
       </c>
       <c r="J83" t="n">
-        <v>43361.33</v>
+        <v>126427.94</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -3690,37 +3690,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v>45823</v>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E84" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F84" t="n">
-        <v>40203.04</v>
+        <v>263106.79</v>
       </c>
       <c r="G84" t="n">
-        <v>704.9299999999999</v>
+        <v>6654.44</v>
       </c>
       <c r="H84" t="n">
-        <v>27214.37</v>
+        <v>177682.51</v>
       </c>
       <c r="I84" t="n">
-        <v>39498.11</v>
+        <v>256452.35</v>
       </c>
       <c r="J84" t="n">
-        <v>39498.11</v>
+        <v>256452.35</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -3729,37 +3729,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v>45825</v>
       </c>
       <c r="D85" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E85" t="n">
-        <v>4200</v>
+        <v>14500</v>
       </c>
       <c r="F85" t="n">
-        <v>311728.22</v>
+        <v>132122.89</v>
       </c>
       <c r="G85" t="n">
-        <v>5465.95</v>
+        <v>3341.62</v>
       </c>
       <c r="H85" t="n">
-        <v>207818.81</v>
+        <v>83829.7</v>
       </c>
       <c r="I85" t="n">
-        <v>306262.27</v>
+        <v>128781.27</v>
       </c>
       <c r="J85" t="n">
-        <v>306262.27</v>
+        <v>128781.27</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
@@ -3768,37 +3768,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v>45827</v>
       </c>
       <c r="D86" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>15400</v>
+        <v>14500</v>
       </c>
       <c r="F86" t="n">
-        <v>1047753.17</v>
+        <v>66061.45</v>
       </c>
       <c r="G86" t="n">
-        <v>27557.5</v>
+        <v>2506.22</v>
       </c>
       <c r="H86" t="n">
-        <v>666752.02</v>
+        <v>41914.85</v>
       </c>
       <c r="I86" t="n">
-        <v>1020195.67</v>
+        <v>63555.23</v>
       </c>
       <c r="J86" t="n">
-        <v>1020195.67</v>
+        <v>63555.23</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -3807,37 +3807,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v>45829</v>
       </c>
       <c r="D87" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>2400</v>
+        <v>14500</v>
       </c>
       <c r="F87" t="n">
-        <v>170708.31</v>
+        <v>264245.78</v>
       </c>
       <c r="G87" t="n">
-        <v>2993.26</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>106692.69</v>
+        <v>167659.39</v>
       </c>
       <c r="I87" t="n">
-        <v>167715.05</v>
+        <v>264245.78</v>
       </c>
       <c r="J87" t="n">
-        <v>167715.05</v>
+        <v>264245.78</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -3846,37 +3846,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v>45831</v>
       </c>
       <c r="D88" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E88" t="n">
-        <v>8900</v>
+        <v>14500</v>
       </c>
       <c r="F88" t="n">
-        <v>192665.36</v>
+        <v>247730.42</v>
       </c>
       <c r="G88" t="n">
-        <v>5067.39</v>
+        <v>6265.55</v>
       </c>
       <c r="H88" t="n">
-        <v>127721.98</v>
+        <v>157180.68</v>
       </c>
       <c r="I88" t="n">
-        <v>187597.97</v>
+        <v>241464.87</v>
       </c>
       <c r="J88" t="n">
-        <v>187597.97</v>
+        <v>241464.87</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -3885,37 +3885,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>45833</v>
       </c>
       <c r="D89" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E89" t="n">
-        <v>2400</v>
+        <v>14500</v>
       </c>
       <c r="F89" t="n">
-        <v>163286.21</v>
+        <v>132122.89</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>102053.88</v>
+        <v>83829.7</v>
       </c>
       <c r="I89" t="n">
-        <v>163286.21</v>
+        <v>132122.89</v>
       </c>
       <c r="J89" t="n">
-        <v>163286.21</v>
+        <v>132122.89</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -3924,37 +3924,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>45835</v>
       </c>
       <c r="D90" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E90" t="n">
-        <v>15400</v>
+        <v>4600</v>
       </c>
       <c r="F90" t="n">
-        <v>619126.87</v>
+        <v>36675.49</v>
       </c>
       <c r="G90" t="n">
-        <v>27139.96</v>
+        <v>1391.38</v>
       </c>
       <c r="H90" t="n">
-        <v>393989.83</v>
+        <v>23121.51</v>
       </c>
       <c r="I90" t="n">
-        <v>591986.91</v>
+        <v>35284.11</v>
       </c>
       <c r="J90" t="n">
-        <v>591986.91</v>
+        <v>35284.11</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -3963,37 +3963,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v>45837</v>
       </c>
       <c r="D91" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E91" t="n">
-        <v>1850</v>
+        <v>8900</v>
       </c>
       <c r="F91" t="n">
-        <v>57212.02</v>
+        <v>30411.05</v>
       </c>
       <c r="G91" t="n">
-        <v>1003.18</v>
+        <v>769.15</v>
       </c>
       <c r="H91" t="n">
-        <v>38656.77</v>
+        <v>20160.13</v>
       </c>
       <c r="I91" t="n">
-        <v>56208.84</v>
+        <v>29641.9</v>
       </c>
       <c r="J91" t="n">
-        <v>56208.84</v>
+        <v>29641.9</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4002,37 +4002,37 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v>45840</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E92" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F92" t="n">
-        <v>141019.91</v>
+        <v>89069.05</v>
       </c>
       <c r="G92" t="n">
-        <v>6181.73</v>
+        <v>3379.07</v>
       </c>
       <c r="H92" t="n">
-        <v>88137.44</v>
+        <v>56152.23</v>
       </c>
       <c r="I92" t="n">
-        <v>134838.18</v>
+        <v>85689.98</v>
       </c>
       <c r="J92" t="n">
-        <v>134838.18</v>
+        <v>85689.98</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4041,37 +4041,37 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v>45842</v>
       </c>
       <c r="D93" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F93" t="n">
-        <v>30152.28</v>
+        <v>175404.53</v>
       </c>
       <c r="G93" t="n">
-        <v>793.05</v>
+        <v>4436.29</v>
       </c>
       <c r="H93" t="n">
-        <v>20410.78</v>
+        <v>118455.01</v>
       </c>
       <c r="I93" t="n">
-        <v>29359.23</v>
+        <v>170968.24</v>
       </c>
       <c r="J93" t="n">
-        <v>29359.23</v>
+        <v>170968.24</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4080,37 +4080,37 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v>45844</v>
       </c>
       <c r="D94" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E94" t="n">
-        <v>1200</v>
+        <v>95000</v>
       </c>
       <c r="F94" t="n">
-        <v>63087.85</v>
+        <v>973836.83</v>
       </c>
       <c r="G94" t="n">
-        <v>1659.31</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>43110.03</v>
+        <v>697062.16</v>
       </c>
       <c r="I94" t="n">
-        <v>61428.54</v>
+        <v>973836.83</v>
       </c>
       <c r="J94" t="n">
-        <v>61428.54</v>
+        <v>973836.83</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4119,37 +4119,37 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v>45846</v>
       </c>
       <c r="D95" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E95" t="n">
-        <v>8900</v>
+        <v>95000</v>
       </c>
       <c r="F95" t="n">
-        <v>605519.6899999999</v>
+        <v>1514857.3</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>38313.45</v>
       </c>
       <c r="H95" t="n">
-        <v>401411.93</v>
+        <v>1084318.91</v>
       </c>
       <c r="I95" t="n">
-        <v>605519.6899999999</v>
+        <v>1476543.85</v>
       </c>
       <c r="J95" t="n">
-        <v>605519.6899999999</v>
+        <v>1476543.85</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4158,37 +4158,37 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v>45848</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E96" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F96" t="n">
-        <v>6030.46</v>
+        <v>54671.54</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>3456.85</v>
       </c>
       <c r="H96" t="n">
-        <v>4082.16</v>
+        <v>35308.7</v>
       </c>
       <c r="I96" t="n">
-        <v>6030.46</v>
+        <v>51214.69</v>
       </c>
       <c r="J96" t="n">
-        <v>6030.46</v>
+        <v>51214.69</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4197,37 +4197,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v>45850</v>
       </c>
       <c r="D97" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F97" t="n">
-        <v>381001.15</v>
+        <v>51937.96</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>242455.28</v>
+        <v>33543.27</v>
       </c>
       <c r="I97" t="n">
-        <v>381001.15</v>
+        <v>51937.96</v>
       </c>
       <c r="J97" t="n">
-        <v>381001.15</v>
+        <v>51937.96</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -4236,37 +4236,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v>45852</v>
       </c>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
-        <v>1850</v>
+        <v>38500</v>
       </c>
       <c r="F98" t="n">
-        <v>11442.4</v>
+        <v>613915.85</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>7731.35</v>
+        <v>414592.52</v>
       </c>
       <c r="I98" t="n">
-        <v>11442.4</v>
+        <v>613915.85</v>
       </c>
       <c r="J98" t="n">
-        <v>11442.4</v>
+        <v>613915.85</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -4275,37 +4275,37 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>45854</v>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F99" t="n">
-        <v>194830.14</v>
+        <v>141918.21</v>
       </c>
       <c r="G99" t="n">
-        <v>5124.33</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>129886.76</v>
+        <v>94080.61</v>
       </c>
       <c r="I99" t="n">
-        <v>189705.81</v>
+        <v>141918.21</v>
       </c>
       <c r="J99" t="n">
-        <v>189705.81</v>
+        <v>141918.21</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4314,37 +4314,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v>45856</v>
       </c>
       <c r="D100" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E100" t="n">
-        <v>1200</v>
+        <v>95000</v>
       </c>
       <c r="F100" t="n">
-        <v>85354.14999999999</v>
+        <v>1190245.02</v>
       </c>
       <c r="G100" t="n">
-        <v>2244.94</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>58325.34</v>
+        <v>851964.86</v>
       </c>
       <c r="I100" t="n">
-        <v>83109.21000000001</v>
+        <v>1190245.02</v>
       </c>
       <c r="J100" t="n">
-        <v>83109.21000000001</v>
+        <v>1190245.02</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4353,37 +4353,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>45858</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E101" t="n">
-        <v>2400</v>
+        <v>95000</v>
       </c>
       <c r="F101" t="n">
-        <v>59376.8</v>
+        <v>1082040.93</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>41050.12</v>
       </c>
       <c r="H101" t="n">
-        <v>37110.5</v>
+        <v>774513.51</v>
       </c>
       <c r="I101" t="n">
-        <v>59376.8</v>
+        <v>1040990.81</v>
       </c>
       <c r="J101" t="n">
-        <v>59376.8</v>
+        <v>1040990.81</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4392,37 +4392,37 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>45860</v>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F102" t="n">
-        <v>143030.06</v>
+        <v>27335.77</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1728.43</v>
       </c>
       <c r="H102" t="n">
-        <v>96641.92999999999</v>
+        <v>17654.35</v>
       </c>
       <c r="I102" t="n">
-        <v>143030.06</v>
+        <v>25607.34</v>
       </c>
       <c r="J102" t="n">
-        <v>143030.06</v>
+        <v>25607.34</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -4431,37 +4431,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D103" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>2400</v>
+        <v>18500</v>
       </c>
       <c r="F103" t="n">
-        <v>59376.8</v>
+        <v>294998.53</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>11191.56</v>
       </c>
       <c r="H103" t="n">
-        <v>37110.5</v>
+        <v>199323.33</v>
       </c>
       <c r="I103" t="n">
-        <v>59376.8</v>
+        <v>283806.97</v>
       </c>
       <c r="J103" t="n">
-        <v>59376.8</v>
+        <v>283806.97</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -4470,37 +4470,37 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v>45864</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E104" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F104" t="n">
-        <v>132979.3</v>
+        <v>2055877.76</v>
       </c>
       <c r="G104" t="n">
-        <v>5829.26</v>
+        <v>51996.82</v>
       </c>
       <c r="H104" t="n">
-        <v>87828.19</v>
+        <v>1471575.66</v>
       </c>
       <c r="I104" t="n">
-        <v>127150.04</v>
+        <v>2003880.94</v>
       </c>
       <c r="J104" t="n">
-        <v>127150.04</v>
+        <v>2003880.94</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4509,37 +4509,37 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>45866</v>
       </c>
       <c r="D105" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>4200</v>
+        <v>95000</v>
       </c>
       <c r="F105" t="n">
-        <v>194830.14</v>
+        <v>108204.09</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>2736.67</v>
       </c>
       <c r="H105" t="n">
-        <v>129886.76</v>
+        <v>77451.35000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>194830.14</v>
+        <v>105467.42</v>
       </c>
       <c r="J105" t="n">
-        <v>194830.14</v>
+        <v>105467.42</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4548,37 +4548,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>45868</v>
       </c>
       <c r="D106" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E106" t="n">
-        <v>21500</v>
+        <v>18500</v>
       </c>
       <c r="F106" t="n">
-        <v>1462772.29</v>
+        <v>294998.53</v>
       </c>
       <c r="G106" t="n">
-        <v>64121.88</v>
+        <v>18652.6</v>
       </c>
       <c r="H106" t="n">
-        <v>966110.0699999999</v>
+        <v>199323.33</v>
       </c>
       <c r="I106" t="n">
-        <v>1398650.41</v>
+        <v>276345.93</v>
       </c>
       <c r="J106" t="n">
-        <v>1398650.41</v>
+        <v>276345.93</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4587,37 +4587,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D107" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E107" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F107" t="n">
-        <v>50253.8</v>
+        <v>41003.66</v>
       </c>
       <c r="G107" t="n">
-        <v>1321.75</v>
+        <v>1555.58</v>
       </c>
       <c r="H107" t="n">
-        <v>34017.96</v>
+        <v>26481.53</v>
       </c>
       <c r="I107" t="n">
-        <v>48932.05</v>
+        <v>39448.08</v>
       </c>
       <c r="J107" t="n">
-        <v>48932.05</v>
+        <v>39448.08</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -4626,37 +4626,37 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v>45872</v>
       </c>
       <c r="D108" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E108" t="n">
-        <v>2400</v>
+        <v>95000</v>
       </c>
       <c r="F108" t="n">
-        <v>133597.81</v>
+        <v>1731265.48</v>
       </c>
       <c r="G108" t="n">
-        <v>3513.82</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>83498.63</v>
+        <v>1239221.61</v>
       </c>
       <c r="I108" t="n">
-        <v>130083.99</v>
+        <v>1731265.48</v>
       </c>
       <c r="J108" t="n">
-        <v>130083.99</v>
+        <v>1731265.48</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
@@ -4665,37 +4665,37 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D109" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E109" t="n">
         <v>8900</v>
       </c>
       <c r="F109" t="n">
-        <v>660566.9300000001</v>
+        <v>172329.26</v>
       </c>
       <c r="G109" t="n">
-        <v>17373.91</v>
+        <v>10896.29</v>
       </c>
       <c r="H109" t="n">
-        <v>437903.92</v>
+        <v>114240.74</v>
       </c>
       <c r="I109" t="n">
-        <v>643193.02</v>
+        <v>161432.97</v>
       </c>
       <c r="J109" t="n">
-        <v>643193.02</v>
+        <v>161432.97</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -4704,37 +4704,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v>45876</v>
       </c>
       <c r="D110" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E110" t="n">
-        <v>15400</v>
+        <v>38500</v>
       </c>
       <c r="F110" t="n">
-        <v>1190628.6</v>
+        <v>350809.06</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>8872.59</v>
       </c>
       <c r="H110" t="n">
-        <v>757672.75</v>
+        <v>236910.01</v>
       </c>
       <c r="I110" t="n">
-        <v>1190628.6</v>
+        <v>341936.47</v>
       </c>
       <c r="J110" t="n">
-        <v>1190628.6</v>
+        <v>341936.47</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4743,37 +4743,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v>45878</v>
       </c>
       <c r="D111" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E111" t="n">
-        <v>15400</v>
+        <v>14500</v>
       </c>
       <c r="F111" t="n">
-        <v>1190628.6</v>
+        <v>115607.53</v>
       </c>
       <c r="G111" t="n">
-        <v>52192.23</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>757672.75</v>
+        <v>73350.98</v>
       </c>
       <c r="I111" t="n">
-        <v>1138436.37</v>
+        <v>115607.53</v>
       </c>
       <c r="J111" t="n">
-        <v>1138436.37</v>
+        <v>115607.53</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -4782,37 +4782,37 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="D112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E112" t="n">
-        <v>1200</v>
+        <v>38500</v>
       </c>
       <c r="F112" t="n">
-        <v>33399.45</v>
+        <v>350809.06</v>
       </c>
       <c r="G112" t="n">
-        <v>878.46</v>
+        <v>13308.88</v>
       </c>
       <c r="H112" t="n">
-        <v>22822.96</v>
+        <v>236910.01</v>
       </c>
       <c r="I112" t="n">
-        <v>32520.99</v>
+        <v>337500.18</v>
       </c>
       <c r="J112" t="n">
-        <v>32520.99</v>
+        <v>337500.18</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v>45882</v>
       </c>
       <c r="D113" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E113" t="n">
-        <v>15400</v>
+        <v>2400</v>
       </c>
       <c r="F113" t="n">
-        <v>381001.15</v>
+        <v>38270.08</v>
       </c>
       <c r="G113" t="n">
-        <v>6680.61</v>
+        <v>2419.8</v>
       </c>
       <c r="H113" t="n">
-        <v>242455.28</v>
+        <v>24716.09</v>
       </c>
       <c r="I113" t="n">
-        <v>374320.54</v>
+        <v>35850.28</v>
       </c>
       <c r="J113" t="n">
-        <v>374320.54</v>
+        <v>35850.28</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -4860,37 +4860,37 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v>45884</v>
       </c>
       <c r="D114" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E114" t="n">
-        <v>650</v>
+        <v>4600</v>
       </c>
       <c r="F114" t="n">
-        <v>36182.74</v>
+        <v>68111.63</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>2584</v>
       </c>
       <c r="H114" t="n">
-        <v>24492.93</v>
+        <v>42939.94</v>
       </c>
       <c r="I114" t="n">
-        <v>36182.74</v>
+        <v>65527.63</v>
       </c>
       <c r="J114" t="n">
-        <v>36182.74</v>
+        <v>65527.63</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -4899,37 +4899,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v>45886</v>
       </c>
       <c r="D115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>8900</v>
+        <v>18500</v>
       </c>
       <c r="F115" t="n">
-        <v>220188.98</v>
+        <v>105356.62</v>
       </c>
       <c r="G115" t="n">
-        <v>5791.3</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>145967.97</v>
+        <v>71186.89999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>214397.68</v>
+        <v>105356.62</v>
       </c>
       <c r="J115" t="n">
-        <v>214397.68</v>
+        <v>105356.62</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -4938,37 +4938,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="D116" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E116" t="n">
-        <v>8900</v>
+        <v>14500</v>
       </c>
       <c r="F116" t="n">
-        <v>633043.3100000001</v>
+        <v>231215.06</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>419657.93</v>
+        <v>146701.97</v>
       </c>
       <c r="I116" t="n">
-        <v>633043.3100000001</v>
+        <v>231215.06</v>
       </c>
       <c r="J116" t="n">
-        <v>633043.3100000001</v>
+        <v>231215.06</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -4977,37 +4977,37 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D117" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E117" t="n">
-        <v>2400</v>
+        <v>14500</v>
       </c>
       <c r="F117" t="n">
-        <v>103909.41</v>
+        <v>280761.15</v>
       </c>
       <c r="G117" t="n">
-        <v>1821.98</v>
+        <v>10651.43</v>
       </c>
       <c r="H117" t="n">
-        <v>64943.38</v>
+        <v>178138.11</v>
       </c>
       <c r="I117" t="n">
-        <v>102087.43</v>
+        <v>270109.72</v>
       </c>
       <c r="J117" t="n">
-        <v>102087.43</v>
+        <v>270109.72</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -5016,37 +5016,37 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v>45892</v>
       </c>
       <c r="D118" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E118" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F118" t="n">
-        <v>930855.09</v>
+        <v>865632.74</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>614797.3199999999</v>
+        <v>619610.8</v>
       </c>
       <c r="I118" t="n">
-        <v>930855.09</v>
+        <v>865632.74</v>
       </c>
       <c r="J118" t="n">
-        <v>930855.09</v>
+        <v>865632.74</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -5055,37 +5055,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v>45894</v>
       </c>
       <c r="D119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E119" t="n">
-        <v>2400</v>
+        <v>18500</v>
       </c>
       <c r="F119" t="n">
-        <v>96487.31</v>
+        <v>316069.85</v>
       </c>
       <c r="G119" t="n">
-        <v>4229.6</v>
+        <v>19984.93</v>
       </c>
       <c r="H119" t="n">
-        <v>60304.57</v>
+        <v>213560.71</v>
       </c>
       <c r="I119" t="n">
-        <v>92257.71000000001</v>
+        <v>296084.92</v>
       </c>
       <c r="J119" t="n">
-        <v>92257.71000000001</v>
+        <v>296084.92</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5094,37 +5094,37 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v>45896</v>
       </c>
       <c r="D120" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E120" t="n">
-        <v>1850</v>
+        <v>14500</v>
       </c>
       <c r="F120" t="n">
-        <v>143030.06</v>
+        <v>247730.42</v>
       </c>
       <c r="G120" t="n">
-        <v>6269.85</v>
+        <v>15663.86</v>
       </c>
       <c r="H120" t="n">
-        <v>96641.92999999999</v>
+        <v>157180.68</v>
       </c>
       <c r="I120" t="n">
-        <v>136760.21</v>
+        <v>232066.56</v>
       </c>
       <c r="J120" t="n">
-        <v>136760.21</v>
+        <v>232066.56</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5133,37 +5133,37 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v>45898</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E121" t="n">
-        <v>21500</v>
+        <v>14500</v>
       </c>
       <c r="F121" t="n">
-        <v>66489.64999999999</v>
+        <v>297276.51</v>
       </c>
       <c r="G121" t="n">
-        <v>1165.85</v>
+        <v>11277.98</v>
       </c>
       <c r="H121" t="n">
-        <v>43914.09</v>
+        <v>188616.82</v>
       </c>
       <c r="I121" t="n">
-        <v>65323.8</v>
+        <v>285998.53</v>
       </c>
       <c r="J121" t="n">
-        <v>65323.8</v>
+        <v>285998.53</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5172,37 +5172,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="D122" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E122" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F122" t="n">
-        <v>103909.41</v>
+        <v>83829.7</v>
       </c>
       <c r="G122" t="n">
-        <v>4554.96</v>
+        <v>3180.3</v>
       </c>
       <c r="H122" t="n">
-        <v>64943.38</v>
+        <v>52849.16</v>
       </c>
       <c r="I122" t="n">
-        <v>99354.45</v>
+        <v>80649.39999999999</v>
       </c>
       <c r="J122" t="n">
-        <v>99354.45</v>
+        <v>80649.39999999999</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -5211,37 +5211,37 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v>45902</v>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E123" t="n">
-        <v>1200</v>
+        <v>14500</v>
       </c>
       <c r="F123" t="n">
-        <v>59376.8</v>
+        <v>132122.89</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>3341.62</v>
       </c>
       <c r="H123" t="n">
-        <v>40574.15</v>
+        <v>83829.7</v>
       </c>
       <c r="I123" t="n">
-        <v>59376.8</v>
+        <v>128781.27</v>
       </c>
       <c r="J123" t="n">
-        <v>59376.8</v>
+        <v>128781.27</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -5250,37 +5250,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v>45904</v>
       </c>
       <c r="D124" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E124" t="n">
-        <v>2400</v>
+        <v>4600</v>
       </c>
       <c r="F124" t="n">
-        <v>118753.61</v>
+        <v>41914.85</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1060.1</v>
       </c>
       <c r="H124" t="n">
-        <v>74221</v>
+        <v>26424.58</v>
       </c>
       <c r="I124" t="n">
-        <v>118753.61</v>
+        <v>40854.75</v>
       </c>
       <c r="J124" t="n">
-        <v>118753.61</v>
+        <v>40854.75</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5289,37 +5289,37 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v>45906</v>
       </c>
       <c r="D125" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E125" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F125" t="n">
-        <v>44223.35</v>
+        <v>438511.32</v>
       </c>
       <c r="G125" t="n">
-        <v>1163.14</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>29935.8</v>
+        <v>296137.52</v>
       </c>
       <c r="I125" t="n">
-        <v>43060.21</v>
+        <v>438511.32</v>
       </c>
       <c r="J125" t="n">
-        <v>43060.21</v>
+        <v>438511.32</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -5328,37 +5328,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D126" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E126" t="n">
         <v>8900</v>
       </c>
       <c r="F126" t="n">
-        <v>412854.33</v>
+        <v>111507.17</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>7050.54</v>
       </c>
       <c r="H126" t="n">
-        <v>273689.95</v>
+        <v>73920.48</v>
       </c>
       <c r="I126" t="n">
-        <v>412854.33</v>
+        <v>104456.63</v>
       </c>
       <c r="J126" t="n">
-        <v>412854.33</v>
+        <v>104456.63</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5367,37 +5367,37 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D127" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E127" t="n">
-        <v>1850</v>
+        <v>18500</v>
       </c>
       <c r="F127" t="n">
-        <v>74375.63</v>
+        <v>105356.62</v>
       </c>
       <c r="G127" t="n">
-        <v>3260.32</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>50253.8</v>
+        <v>71186.89999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>71115.31</v>
+        <v>105356.62</v>
       </c>
       <c r="J127" t="n">
-        <v>71115.31</v>
+        <v>105356.62</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5406,37 +5406,37 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v>45912</v>
       </c>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E128" t="n">
-        <v>1850</v>
+        <v>4600</v>
       </c>
       <c r="F128" t="n">
-        <v>17163.61</v>
+        <v>26196.78</v>
       </c>
       <c r="G128" t="n">
-        <v>451.43</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>11597.03</v>
+        <v>16515.36</v>
       </c>
       <c r="I128" t="n">
-        <v>16712.18</v>
+        <v>26196.78</v>
       </c>
       <c r="J128" t="n">
-        <v>16712.18</v>
+        <v>26196.78</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -5445,37 +5445,37 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v>45914</v>
       </c>
       <c r="D129" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E129" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F129" t="n">
-        <v>398937.9</v>
+        <v>38270.08</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>967.92</v>
       </c>
       <c r="H129" t="n">
-        <v>263484.56</v>
+        <v>24716.09</v>
       </c>
       <c r="I129" t="n">
-        <v>398937.9</v>
+        <v>37302.16</v>
       </c>
       <c r="J129" t="n">
-        <v>398937.9</v>
+        <v>37302.16</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5484,37 +5484,37 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v>45916</v>
       </c>
       <c r="D130" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
         <v>2400</v>
       </c>
       <c r="F130" t="n">
-        <v>81643.10000000001</v>
+        <v>5467.15</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>51026.94</v>
+        <v>3530.87</v>
       </c>
       <c r="I130" t="n">
-        <v>81643.10000000001</v>
+        <v>5467.15</v>
       </c>
       <c r="J130" t="n">
-        <v>81643.10000000001</v>
+        <v>5467.15</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5523,37 +5523,37 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v>45918</v>
       </c>
       <c r="D131" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E131" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F131" t="n">
-        <v>22111.67</v>
+        <v>51937.96</v>
       </c>
       <c r="G131" t="n">
-        <v>581.5700000000001</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>14967.9</v>
+        <v>33543.27</v>
       </c>
       <c r="I131" t="n">
-        <v>21530.1</v>
+        <v>51937.96</v>
       </c>
       <c r="J131" t="n">
-        <v>21530.1</v>
+        <v>51937.96</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5562,37 +5562,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v>45920</v>
       </c>
       <c r="D132" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
         <v>2400</v>
       </c>
       <c r="F132" t="n">
-        <v>66798.89999999999</v>
+        <v>2733.58</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>69.14</v>
       </c>
       <c r="H132" t="n">
-        <v>41749.31</v>
+        <v>1765.44</v>
       </c>
       <c r="I132" t="n">
-        <v>66798.89999999999</v>
+        <v>2664.44</v>
       </c>
       <c r="J132" t="n">
-        <v>66798.89999999999</v>
+        <v>2664.44</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5601,37 +5601,37 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v>45922</v>
       </c>
       <c r="D133" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E133" t="n">
-        <v>1850</v>
+        <v>14500</v>
       </c>
       <c r="F133" t="n">
-        <v>137308.86</v>
+        <v>214699.7</v>
       </c>
       <c r="G133" t="n">
-        <v>6019.05</v>
+        <v>8145.21</v>
       </c>
       <c r="H133" t="n">
-        <v>92776.25</v>
+        <v>136223.26</v>
       </c>
       <c r="I133" t="n">
-        <v>131289.81</v>
+        <v>206554.49</v>
       </c>
       <c r="J133" t="n">
-        <v>131289.81</v>
+        <v>206554.49</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -5640,12 +5640,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Anadolu Sanayi Grubu A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
@@ -5655,22 +5655,22 @@
         <v>8</v>
       </c>
       <c r="E134" t="n">
-        <v>650</v>
+        <v>2400</v>
       </c>
       <c r="F134" t="n">
-        <v>16081.22</v>
+        <v>21868.62</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>553.1</v>
       </c>
       <c r="H134" t="n">
-        <v>10885.75</v>
+        <v>14123.48</v>
       </c>
       <c r="I134" t="n">
-        <v>16081.22</v>
+        <v>21315.52</v>
       </c>
       <c r="J134" t="n">
-        <v>16081.22</v>
+        <v>21315.52</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5679,37 +5679,37 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v>45926</v>
       </c>
       <c r="D135" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>1850</v>
+        <v>2400</v>
       </c>
       <c r="F135" t="n">
-        <v>143030.06</v>
+        <v>2733.58</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>103.71</v>
       </c>
       <c r="H135" t="n">
-        <v>96641.92999999999</v>
+        <v>1765.44</v>
       </c>
       <c r="I135" t="n">
-        <v>143030.06</v>
+        <v>2629.87</v>
       </c>
       <c r="J135" t="n">
-        <v>143030.06</v>
+        <v>2629.87</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -5718,37 +5718,37 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v>45928</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E136" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F136" t="n">
-        <v>3711.05</v>
+        <v>68111.63</v>
       </c>
       <c r="G136" t="n">
-        <v>162.68</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>2535.88</v>
+        <v>42939.94</v>
       </c>
       <c r="I136" t="n">
-        <v>3548.37</v>
+        <v>68111.63</v>
       </c>
       <c r="J136" t="n">
-        <v>3548.37</v>
+        <v>68111.63</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -5757,37 +5757,37 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="D137" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E137" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="F137" t="n">
-        <v>18555.25</v>
+        <v>421426.47</v>
       </c>
       <c r="G137" t="n">
-        <v>488.03</v>
+        <v>26646.57</v>
       </c>
       <c r="H137" t="n">
-        <v>12679.42</v>
+        <v>284747.61</v>
       </c>
       <c r="I137" t="n">
-        <v>18067.22</v>
+        <v>394779.9</v>
       </c>
       <c r="J137" t="n">
-        <v>18067.22</v>
+        <v>394779.9</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5796,12 +5796,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
@@ -5811,22 +5811,22 @@
         <v>19</v>
       </c>
       <c r="E138" t="n">
-        <v>4200</v>
+        <v>2400</v>
       </c>
       <c r="F138" t="n">
-        <v>246784.84</v>
+        <v>51937.96</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>3284.01</v>
       </c>
       <c r="H138" t="n">
-        <v>164523.23</v>
+        <v>33543.27</v>
       </c>
       <c r="I138" t="n">
-        <v>246784.84</v>
+        <v>48653.95</v>
       </c>
       <c r="J138" t="n">
-        <v>246784.84</v>
+        <v>48653.95</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -5835,37 +5835,37 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v>45935</v>
       </c>
       <c r="D139" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E139" t="n">
-        <v>15400</v>
+        <v>38500</v>
       </c>
       <c r="F139" t="n">
-        <v>1190628.6</v>
+        <v>613915.85</v>
       </c>
       <c r="G139" t="n">
-        <v>20876.89</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>757672.75</v>
+        <v>414592.52</v>
       </c>
       <c r="I139" t="n">
-        <v>1169751.71</v>
+        <v>613915.85</v>
       </c>
       <c r="J139" t="n">
-        <v>1169751.71</v>
+        <v>613915.85</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -5874,37 +5874,37 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v>45937</v>
       </c>
       <c r="D140" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
-        <v>4200</v>
+        <v>18500</v>
       </c>
       <c r="F140" t="n">
-        <v>324716.89</v>
+        <v>42142.65</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1065.86</v>
       </c>
       <c r="H140" t="n">
-        <v>216477.93</v>
+        <v>28474.76</v>
       </c>
       <c r="I140" t="n">
-        <v>324716.89</v>
+        <v>41076.79</v>
       </c>
       <c r="J140" t="n">
-        <v>324716.89</v>
+        <v>41076.79</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -5913,37 +5913,37 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v>45939</v>
       </c>
       <c r="D141" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E141" t="n">
-        <v>4200</v>
+        <v>8900</v>
       </c>
       <c r="F141" t="n">
-        <v>246784.84</v>
+        <v>70959.11</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>2692.02</v>
       </c>
       <c r="H141" t="n">
-        <v>164523.23</v>
+        <v>47040.31</v>
       </c>
       <c r="I141" t="n">
-        <v>246784.84</v>
+        <v>68267.09</v>
       </c>
       <c r="J141" t="n">
-        <v>246784.84</v>
+        <v>68267.09</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -5952,37 +5952,37 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Gaziantep İhracat ve Toptan</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v>45941</v>
       </c>
       <c r="D142" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E142" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F142" t="n">
-        <v>904877.74</v>
+        <v>131781.2</v>
       </c>
       <c r="G142" t="n">
-        <v>23799.66</v>
+        <v>3332.98</v>
       </c>
       <c r="H142" t="n">
-        <v>575831.29</v>
+        <v>87360.57000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>881078.08</v>
+        <v>128448.22</v>
       </c>
       <c r="J142" t="n">
-        <v>881078.08</v>
+        <v>128448.22</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -5991,12 +5991,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
@@ -6006,22 +6006,22 @@
         <v>3</v>
       </c>
       <c r="E143" t="n">
-        <v>1200</v>
+        <v>8900</v>
       </c>
       <c r="F143" t="n">
-        <v>11133.15</v>
+        <v>30411.05</v>
       </c>
       <c r="G143" t="n">
-        <v>488.03</v>
+        <v>1153.72</v>
       </c>
       <c r="H143" t="n">
-        <v>7607.65</v>
+        <v>20160.13</v>
       </c>
       <c r="I143" t="n">
-        <v>10645.12</v>
+        <v>29257.33</v>
       </c>
       <c r="J143" t="n">
-        <v>10645.12</v>
+        <v>29257.33</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6030,480 +6030,480 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v>45945</v>
       </c>
       <c r="D144" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E144" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F144" t="n">
-        <v>14844.2</v>
+        <v>94308.41</v>
       </c>
       <c r="G144" t="n">
-        <v>260.28</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>10143.54</v>
+        <v>59455.3</v>
       </c>
       <c r="I144" t="n">
-        <v>14583.92</v>
+        <v>94308.41</v>
       </c>
       <c r="J144" t="n">
-        <v>4375.18</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>10208.74</v>
+        <v>94308.41</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v>45947</v>
       </c>
       <c r="D145" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E145" t="n">
-        <v>4200</v>
+        <v>18500</v>
       </c>
       <c r="F145" t="n">
-        <v>246784.84</v>
+        <v>63213.97</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>164523.23</v>
+        <v>42712.14</v>
       </c>
       <c r="I145" t="n">
-        <v>246784.84</v>
+        <v>63213.97</v>
       </c>
       <c r="J145" t="n">
-        <v>74035.45</v>
+        <v>31606.99</v>
       </c>
       <c r="K145" t="n">
-        <v>172749.39</v>
+        <v>31606.98</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v>45949</v>
       </c>
       <c r="D146" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E146" t="n">
-        <v>2400</v>
+        <v>18500</v>
       </c>
       <c r="F146" t="n">
-        <v>163286.21</v>
+        <v>147499.26</v>
       </c>
       <c r="G146" t="n">
-        <v>2863.12</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>102053.88</v>
+        <v>99661.66</v>
       </c>
       <c r="I146" t="n">
-        <v>160423.09</v>
+        <v>147499.26</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>73749.63</v>
       </c>
       <c r="K146" t="n">
-        <v>160423.09</v>
+        <v>73749.63</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v>45951</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E147" t="n">
-        <v>650</v>
+        <v>18500</v>
       </c>
       <c r="F147" t="n">
-        <v>2010.15</v>
+        <v>105356.62</v>
       </c>
       <c r="G147" t="n">
-        <v>52.87</v>
+        <v>3996.99</v>
       </c>
       <c r="H147" t="n">
-        <v>1360.72</v>
+        <v>71186.89999999999</v>
       </c>
       <c r="I147" t="n">
-        <v>1957.28</v>
+        <v>101359.63</v>
       </c>
       <c r="J147" t="n">
-        <v>978.64</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>978.64</v>
+        <v>101359.63</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D148" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E148" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F148" t="n">
-        <v>265958.6</v>
+        <v>757428.65</v>
       </c>
       <c r="G148" t="n">
-        <v>6995.11</v>
+        <v>28735.09</v>
       </c>
       <c r="H148" t="n">
-        <v>175656.38</v>
+        <v>542159.45</v>
       </c>
       <c r="I148" t="n">
-        <v>258963.49</v>
+        <v>728693.5600000001</v>
       </c>
       <c r="J148" t="n">
-        <v>129481.74</v>
+        <v>218608.07</v>
       </c>
       <c r="K148" t="n">
-        <v>129481.75</v>
+        <v>510085.49</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v>45955</v>
       </c>
       <c r="D149" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E149" t="n">
-        <v>21500</v>
+        <v>14500</v>
       </c>
       <c r="F149" t="n">
-        <v>1529261.93</v>
+        <v>198184.34</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>1010024.16</v>
+        <v>125744.55</v>
       </c>
       <c r="I149" t="n">
-        <v>1529261.93</v>
+        <v>198184.34</v>
       </c>
       <c r="J149" t="n">
-        <v>764630.96</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>764630.97</v>
+        <v>198184.34</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Akdeniz Endüstriyel Ürünler</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v>45957</v>
       </c>
       <c r="D150" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E150" t="n">
-        <v>8900</v>
+        <v>14500</v>
       </c>
       <c r="F150" t="n">
-        <v>660566.9300000001</v>
+        <v>99092.17</v>
       </c>
       <c r="G150" t="n">
-        <v>28956.52</v>
+        <v>2506.22</v>
       </c>
       <c r="H150" t="n">
-        <v>437903.92</v>
+        <v>62872.27</v>
       </c>
       <c r="I150" t="n">
-        <v>631610.41</v>
+        <v>96585.95</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>631610.41</v>
+        <v>96585.95</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="D151" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>15400</v>
+        <v>95000</v>
       </c>
       <c r="F151" t="n">
-        <v>952502.88</v>
+        <v>108204.09</v>
       </c>
       <c r="G151" t="n">
-        <v>41753.78</v>
+        <v>2736.67</v>
       </c>
       <c r="H151" t="n">
-        <v>606138.2</v>
+        <v>77451.35000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>910749.1</v>
+        <v>105467.42</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>52733.71</v>
       </c>
       <c r="K151" t="n">
-        <v>910749.1</v>
+        <v>52733.71</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D152" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E152" t="n">
-        <v>21500</v>
+        <v>2400</v>
       </c>
       <c r="F152" t="n">
-        <v>997344.74</v>
+        <v>19135.04</v>
       </c>
       <c r="G152" t="n">
-        <v>26231.68</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>658711.41</v>
+        <v>12358.05</v>
       </c>
       <c r="I152" t="n">
-        <v>971113.0600000001</v>
+        <v>19135.04</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>5740.51</v>
       </c>
       <c r="K152" t="n">
-        <v>971113.0600000001</v>
+        <v>13394.53</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v>45963</v>
       </c>
       <c r="D153" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E153" t="n">
-        <v>15400</v>
+        <v>38500</v>
       </c>
       <c r="F153" t="n">
-        <v>523876.59</v>
+        <v>438511.32</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>27726.84</v>
       </c>
       <c r="H153" t="n">
-        <v>333376.01</v>
+        <v>296137.52</v>
       </c>
       <c r="I153" t="n">
-        <v>523876.59</v>
+        <v>410784.48</v>
       </c>
       <c r="J153" t="n">
-        <v>261938.3</v>
+        <v>205392.24</v>
       </c>
       <c r="K153" t="n">
-        <v>261938.29</v>
+        <v>205392.24</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Adana Bölge Bayi A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Ürün Beta Premium</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E154" t="n">
-        <v>4200</v>
+        <v>14500</v>
       </c>
       <c r="F154" t="n">
-        <v>116898.08</v>
+        <v>313791.87</v>
       </c>
       <c r="G154" t="n">
-        <v>3074.6</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>77932.05</v>
+        <v>199095.53</v>
       </c>
       <c r="I154" t="n">
-        <v>113823.48</v>
+        <v>313791.87</v>
       </c>
       <c r="J154" t="n">
-        <v>34147.04</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>79676.44</v>
+        <v>313791.87</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v>45967</v>
       </c>
       <c r="D155" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E155" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F155" t="n">
-        <v>1263303.34</v>
+        <v>1514857.3</v>
       </c>
       <c r="G155" t="n">
-        <v>55377.99</v>
+        <v>38313.45</v>
       </c>
       <c r="H155" t="n">
-        <v>834367.79</v>
+        <v>1084318.91</v>
       </c>
       <c r="I155" t="n">
-        <v>1207925.35</v>
+        <v>1476543.85</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>738271.9300000001</v>
       </c>
       <c r="K155" t="n">
-        <v>1207925.35</v>
+        <v>738271.92</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Müşteri Grubu B - Makine</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
@@ -6513,1000 +6513,1000 @@
         <v>11</v>
       </c>
       <c r="E156" t="n">
-        <v>2400</v>
+        <v>95000</v>
       </c>
       <c r="F156" t="n">
-        <v>81643.10000000001</v>
+        <v>1190245.02</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>51026.94</v>
+        <v>851964.86</v>
       </c>
       <c r="I156" t="n">
-        <v>81643.10000000001</v>
+        <v>1190245.02</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>357073.51</v>
       </c>
       <c r="K156" t="n">
-        <v>81643.10000000001</v>
+        <v>833171.51</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v>45971</v>
       </c>
       <c r="D157" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E157" t="n">
-        <v>650</v>
+        <v>14500</v>
       </c>
       <c r="F157" t="n">
-        <v>12060.91</v>
+        <v>264245.78</v>
       </c>
       <c r="G157" t="n">
-        <v>317.22</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>8164.31</v>
+        <v>167659.39</v>
       </c>
       <c r="I157" t="n">
-        <v>11743.69</v>
+        <v>264245.78</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>11743.69</v>
+        <v>264245.78</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Toroslar Lojistik ve Ticaret</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v>45973</v>
       </c>
       <c r="D158" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E158" t="n">
-        <v>650</v>
+        <v>8900</v>
       </c>
       <c r="F158" t="n">
-        <v>18091.37</v>
+        <v>152055.23</v>
       </c>
       <c r="G158" t="n">
-        <v>317.22</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>12246.47</v>
+        <v>100800.65</v>
       </c>
       <c r="I158" t="n">
-        <v>17774.15</v>
+        <v>152055.23</v>
       </c>
       <c r="J158" t="n">
-        <v>8887.08</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>8887.07</v>
+        <v>152055.23</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v>45975</v>
       </c>
       <c r="D159" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E159" t="n">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="F159" t="n">
-        <v>857252.6</v>
+        <v>358212.5</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>9059.83</v>
       </c>
       <c r="H159" t="n">
-        <v>545524.38</v>
+        <v>242035.47</v>
       </c>
       <c r="I159" t="n">
-        <v>857252.6</v>
+        <v>349152.67</v>
       </c>
       <c r="J159" t="n">
-        <v>257175.78</v>
+        <v>174576.33</v>
       </c>
       <c r="K159" t="n">
-        <v>600076.8199999999</v>
+        <v>174576.34</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v>45977</v>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E160" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F160" t="n">
-        <v>11133.15</v>
+        <v>38270.08</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>2419.8</v>
       </c>
       <c r="H160" t="n">
-        <v>7607.65</v>
+        <v>24716.09</v>
       </c>
       <c r="I160" t="n">
-        <v>11133.15</v>
+        <v>35850.28</v>
       </c>
       <c r="J160" t="n">
-        <v>5566.57</v>
+        <v>10755.08</v>
       </c>
       <c r="K160" t="n">
-        <v>5566.58</v>
+        <v>25095.2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v>45979</v>
       </c>
       <c r="D161" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E161" t="n">
-        <v>2400</v>
+        <v>8900</v>
       </c>
       <c r="F161" t="n">
-        <v>118753.61</v>
+        <v>81096.12</v>
       </c>
       <c r="G161" t="n">
-        <v>5205.67</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>74221</v>
+        <v>53760.35</v>
       </c>
       <c r="I161" t="n">
-        <v>113547.94</v>
+        <v>81096.12</v>
       </c>
       <c r="J161" t="n">
-        <v>56773.97</v>
+        <v>24328.84</v>
       </c>
       <c r="K161" t="n">
-        <v>56773.97</v>
+        <v>56767.28</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Çelik Bağlantı Flanşı Q120</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D162" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E162" t="n">
-        <v>1200</v>
+        <v>2400</v>
       </c>
       <c r="F162" t="n">
-        <v>85354.14999999999</v>
+        <v>21868.62</v>
       </c>
       <c r="G162" t="n">
-        <v>2244.94</v>
+        <v>829.64</v>
       </c>
       <c r="H162" t="n">
-        <v>58325.34</v>
+        <v>14123.48</v>
       </c>
       <c r="I162" t="n">
-        <v>83109.21000000001</v>
+        <v>21038.98</v>
       </c>
       <c r="J162" t="n">
-        <v>41554.61</v>
+        <v>6311.69</v>
       </c>
       <c r="K162" t="n">
-        <v>41554.6</v>
+        <v>14727.29</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v>45983</v>
       </c>
       <c r="D163" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F163" t="n">
-        <v>997344.74</v>
+        <v>10137.02</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>384.57</v>
       </c>
       <c r="H163" t="n">
-        <v>658711.41</v>
+        <v>6720.04</v>
       </c>
       <c r="I163" t="n">
-        <v>997344.74</v>
+        <v>9752.450000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>2925.74</v>
       </c>
       <c r="K163" t="n">
-        <v>997344.74</v>
+        <v>6826.71</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v>45985</v>
       </c>
       <c r="D164" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E164" t="n">
-        <v>15400</v>
+        <v>18500</v>
       </c>
       <c r="F164" t="n">
-        <v>381001.15</v>
+        <v>337141.17</v>
       </c>
       <c r="G164" t="n">
-        <v>10020.91</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>242455.28</v>
+        <v>227798.09</v>
       </c>
       <c r="I164" t="n">
-        <v>370980.24</v>
+        <v>337141.17</v>
       </c>
       <c r="J164" t="n">
-        <v>185490.12</v>
+        <v>101142.35</v>
       </c>
       <c r="K164" t="n">
-        <v>185490.12</v>
+        <v>235998.82</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v>45987</v>
       </c>
       <c r="D165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E165" t="n">
-        <v>1200</v>
+        <v>14500</v>
       </c>
       <c r="F165" t="n">
-        <v>37110.5</v>
+        <v>148638.25</v>
       </c>
       <c r="G165" t="n">
-        <v>1626.77</v>
+        <v>3759.33</v>
       </c>
       <c r="H165" t="n">
-        <v>25358.84</v>
+        <v>94308.41</v>
       </c>
       <c r="I165" t="n">
-        <v>35483.73</v>
+        <v>144878.92</v>
       </c>
       <c r="J165" t="n">
-        <v>10645.12</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>24838.61</v>
+        <v>144878.92</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v>45989</v>
       </c>
       <c r="D166" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E166" t="n">
-        <v>21500</v>
+        <v>95000</v>
       </c>
       <c r="F166" t="n">
-        <v>1196813.69</v>
+        <v>973836.83</v>
       </c>
       <c r="G166" t="n">
-        <v>52463.36</v>
+        <v>61575.18</v>
       </c>
       <c r="H166" t="n">
-        <v>790453.6899999999</v>
+        <v>697062.16</v>
       </c>
       <c r="I166" t="n">
-        <v>1144350.33</v>
+        <v>912261.65</v>
       </c>
       <c r="J166" t="n">
-        <v>343305.1</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>801045.23</v>
+        <v>912261.65</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Müşteri Grubu A - Makine</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Yedek Parça Servis Paketi</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="D167" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="E167" t="n">
-        <v>2400</v>
+        <v>95000</v>
       </c>
       <c r="F167" t="n">
-        <v>178130.41</v>
+        <v>757428.65</v>
       </c>
       <c r="G167" t="n">
-        <v>7808.5</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>111331.51</v>
+        <v>542159.45</v>
       </c>
       <c r="I167" t="n">
-        <v>170321.91</v>
+        <v>757428.65</v>
       </c>
       <c r="J167" t="n">
-        <v>51096.57</v>
+        <v>227228.6</v>
       </c>
       <c r="K167" t="n">
-        <v>119225.34</v>
+        <v>530200.05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>İç Anadolu Tüketim Malları</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v>45993</v>
       </c>
       <c r="D168" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E168" t="n">
-        <v>650</v>
+        <v>4600</v>
       </c>
       <c r="F168" t="n">
-        <v>46233.5</v>
+        <v>73350.98</v>
       </c>
       <c r="G168" t="n">
-        <v>1216.01</v>
+        <v>2782.77</v>
       </c>
       <c r="H168" t="n">
-        <v>31296.52</v>
+        <v>46243.01</v>
       </c>
       <c r="I168" t="n">
-        <v>45017.49</v>
+        <v>70568.21000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>13505.25</v>
+        <v>21170.46</v>
       </c>
       <c r="K168" t="n">
-        <v>31512.24</v>
+        <v>49397.75</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v>45995</v>
       </c>
       <c r="D169" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E169" t="n">
-        <v>15400</v>
+        <v>4600</v>
       </c>
       <c r="F169" t="n">
-        <v>428626.3</v>
+        <v>83829.7</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>3180.3</v>
       </c>
       <c r="H169" t="n">
-        <v>272762.19</v>
+        <v>52849.16</v>
       </c>
       <c r="I169" t="n">
-        <v>428626.3</v>
+        <v>80649.39999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>214313.15</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>214313.15</v>
+        <v>80649.39999999999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ege Dağıtım ve Ticaret Ltd.</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Talaşlı İmalat Revizyon Paketi</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v>45997</v>
       </c>
       <c r="D170" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>1200</v>
+        <v>14500</v>
       </c>
       <c r="F170" t="n">
-        <v>40821.55</v>
+        <v>16515.36</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>27894.73</v>
+        <v>10478.71</v>
       </c>
       <c r="I170" t="n">
-        <v>40821.55</v>
+        <v>16515.36</v>
       </c>
       <c r="J170" t="n">
-        <v>12246.47</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>28575.08</v>
+        <v>16515.36</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Ürün Gamma Endüstriyel</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v>45999</v>
       </c>
       <c r="D171" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E171" t="n">
-        <v>8900</v>
+        <v>18500</v>
       </c>
       <c r="F171" t="n">
-        <v>192665.36</v>
+        <v>273927.2</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>127721.98</v>
+        <v>185085.95</v>
       </c>
       <c r="I171" t="n">
-        <v>192665.36</v>
+        <v>273927.2</v>
       </c>
       <c r="J171" t="n">
-        <v>57799.61</v>
+        <v>82178.16</v>
       </c>
       <c r="K171" t="n">
-        <v>134865.75</v>
+        <v>191749.04</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Bursa İmalat Tedarik Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v>46001</v>
       </c>
       <c r="D172" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E172" t="n">
-        <v>21500</v>
+        <v>4600</v>
       </c>
       <c r="F172" t="n">
-        <v>598406.84</v>
+        <v>99547.77</v>
       </c>
       <c r="G172" t="n">
-        <v>26231.68</v>
+        <v>2517.74</v>
       </c>
       <c r="H172" t="n">
-        <v>395226.85</v>
+        <v>62758.37</v>
       </c>
       <c r="I172" t="n">
-        <v>572175.16</v>
+        <v>97030.03</v>
       </c>
       <c r="J172" t="n">
-        <v>286087.58</v>
+        <v>29109.01</v>
       </c>
       <c r="K172" t="n">
-        <v>286087.58</v>
+        <v>67921.02</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Kocaeli Ağır Sanayi Pazarlama</t>
+          <t>Ulusal Hesap H - Makine</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Özel İmalat Pres Gövdesi</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v>46003</v>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E173" t="n">
-        <v>15400</v>
+        <v>95000</v>
       </c>
       <c r="F173" t="n">
-        <v>190500.58</v>
+        <v>1839469.58</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>46523.47</v>
       </c>
       <c r="H173" t="n">
-        <v>121227.64</v>
+        <v>1316672.96</v>
       </c>
       <c r="I173" t="n">
-        <v>190500.58</v>
+        <v>1792946.11</v>
       </c>
       <c r="J173" t="n">
-        <v>95250.28999999999</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>95250.28999999999</v>
+        <v>1792946.11</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Ticari Kanal G - Makine</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Ürün Delta Kompakt</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v>46005</v>
       </c>
       <c r="D174" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E174" t="n">
-        <v>1200</v>
+        <v>4600</v>
       </c>
       <c r="F174" t="n">
-        <v>44532.6</v>
+        <v>94308.41</v>
       </c>
       <c r="G174" t="n">
-        <v>0</v>
+        <v>2385.23</v>
       </c>
       <c r="H174" t="n">
-        <v>30430.61</v>
+        <v>59455.3</v>
       </c>
       <c r="I174" t="n">
-        <v>44532.6</v>
+        <v>91923.17999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>45961.59</v>
       </c>
       <c r="K174" t="n">
-        <v>44532.6</v>
+        <v>45961.59</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Toptan Müşteri F - Makine</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Ürün Alpha Standart</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v>46007</v>
       </c>
       <c r="D175" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E175" t="n">
-        <v>1850</v>
+        <v>4600</v>
       </c>
       <c r="F175" t="n">
-        <v>131587.65</v>
+        <v>78590.34</v>
       </c>
       <c r="G175" t="n">
-        <v>5768.26</v>
+        <v>1987.69</v>
       </c>
       <c r="H175" t="n">
-        <v>88910.58</v>
+        <v>49546.08</v>
       </c>
       <c r="I175" t="n">
-        <v>125819.39</v>
+        <v>76602.64999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>62909.69</v>
+        <v>38301.32</v>
       </c>
       <c r="K175" t="n">
-        <v>62909.7</v>
+        <v>38301.33</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Marmara Perakende Çözümleri</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D176" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E176" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F176" t="n">
-        <v>95250.28999999999</v>
+        <v>81096.12</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>60613.82</v>
+        <v>53760.35</v>
       </c>
       <c r="I176" t="n">
-        <v>95250.28999999999</v>
+        <v>81096.12</v>
       </c>
       <c r="J176" t="n">
-        <v>47625.14</v>
+        <v>40548.06</v>
       </c>
       <c r="K176" t="n">
-        <v>47625.15</v>
+        <v>40548.06</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>İstanbul Kurumsal Tedarik A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v>46011</v>
       </c>
       <c r="D177" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E177" t="n">
-        <v>15400</v>
+        <v>8900</v>
       </c>
       <c r="F177" t="n">
-        <v>1095378.32</v>
+        <v>40548.06</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>2563.83</v>
       </c>
       <c r="H177" t="n">
-        <v>697058.9300000001</v>
+        <v>26880.17</v>
       </c>
       <c r="I177" t="n">
-        <v>1095378.32</v>
+        <v>37984.23</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>1095378.32</v>
+        <v>37984.23</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>İzmir Ticari Faaliyetler A.Ş.</t>
+          <t>Bölge Bayi C - Makine</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>Hidrolik Silindir Pistonu 50T</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v>46013</v>
       </c>
       <c r="D178" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E178" t="n">
-        <v>21500</v>
+        <v>18500</v>
       </c>
       <c r="F178" t="n">
-        <v>265958.6</v>
+        <v>147499.26</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>5595.78</v>
       </c>
       <c r="H178" t="n">
-        <v>175656.38</v>
+        <v>99661.66</v>
       </c>
       <c r="I178" t="n">
-        <v>265958.6</v>
+        <v>141903.48</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>265958.6</v>
+        <v>141903.48</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ankara Proje Yönetim ve Satış</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Ürün Epsilon Profesyonel</t>
+          <t>Yedek Dişli Takımı Çelik</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v>46015</v>
       </c>
       <c r="D179" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E179" t="n">
-        <v>15400</v>
+        <v>4600</v>
       </c>
       <c r="F179" t="n">
-        <v>762002.3100000001</v>
+        <v>99547.77</v>
       </c>
       <c r="G179" t="n">
-        <v>20041.82</v>
+        <v>6294.35</v>
       </c>
       <c r="H179" t="n">
-        <v>484910.56</v>
+        <v>62758.37</v>
       </c>
       <c r="I179" t="n">
-        <v>741960.49</v>
+        <v>93253.42</v>
       </c>
       <c r="J179" t="n">
-        <v>370980.24</v>
+        <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>370980.25</v>
+        <v>93253.42</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Güneydoğu Pazarlama Ltd.</t>
+          <t>Stratejik Ortak E - Makine</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Ürün Zeta Hızlı Tüketim</t>
+          <t>Ağır Sanayi Redüktörü 15kW</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v>46017</v>
       </c>
       <c r="D180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E180" t="n">
-        <v>650</v>
+        <v>38500</v>
       </c>
       <c r="F180" t="n">
-        <v>12060.91</v>
+        <v>306957.93</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>7763.51</v>
       </c>
       <c r="H180" t="n">
-        <v>8164.31</v>
+        <v>207296.26</v>
       </c>
       <c r="I180" t="n">
-        <v>12060.91</v>
+        <v>299194.42</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>149597.21</v>
       </c>
       <c r="K180" t="n">
-        <v>12060.91</v>
+        <v>149597.21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Karadeniz Toptan Dağıtım A.Ş.</t>
+          <t>Kurumsal Müşteri D - Makine</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Özel Sipariş Modeli X</t>
+          <t>CNC Talaşlı İmalat Şaft Grubu</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v>46019</v>
       </c>
       <c r="D181" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E181" t="n">
-        <v>21500</v>
+        <v>8900</v>
       </c>
       <c r="F181" t="n">
-        <v>265958.6</v>
+        <v>60822.09</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1538.3</v>
       </c>
       <c r="H181" t="n">
-        <v>175656.38</v>
+        <v>40320.26</v>
       </c>
       <c r="I181" t="n">
-        <v>265958.6</v>
+        <v>59283.79</v>
       </c>
       <c r="J181" t="n">
-        <v>79787.58</v>
+        <v>17785.14</v>
       </c>
       <c r="K181" t="n">
-        <v>186171.02</v>
+        <v>41498.65</v>
       </c>
     </row>
   </sheetData>
